--- a/FIA2026-2.xlsx
+++ b/FIA2026-2.xlsx
@@ -245,7 +245,7 @@
     <x:row r="2">
       <x:c r="A2" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Extraído de: HORARIOS 26-2 (1).xlsx</x:t>
+          <x:t xml:space="preserve">Extraído de: HORARIOS 26-2 (2).xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" s="2" t="n"/>
@@ -6982,7 +6982,7 @@
       </x:c>
       <x:c r="E185" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 08-09</x:t>
+          <x:t xml:space="preserve">JU 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F185" s="7" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </x:c>
       <x:c r="E197" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 17-18</x:t>
+          <x:t xml:space="preserve">LU 17-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F197" s="7" t="inlineStr">
@@ -18236,7 +18236,7 @@
       </x:c>
       <x:c r="B1" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HORARIOS 26-2 (1).xlsx</x:t>
+          <x:t xml:space="preserve">HORARIOS 26-2 (2).xlsx</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -18270,7 +18270,7 @@
       </x:c>
       <x:c r="B4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HORARIOS 26-2 (1).xlsx</x:t>
+          <x:t xml:space="preserve">HORARIOS 26-2 (2).xlsx</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/FIA2026-2.xlsx
+++ b/FIA2026-2.xlsx
@@ -91,8 +91,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HorariosUNI" displayName="HorariosUNI" ref="A4:G488" headerRowCount="1">
-  <x:autoFilter ref="A4:G488"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HorariosUNI" displayName="HorariosUNI" ref="A4:G502" headerRowCount="1">
+  <x:autoFilter ref="A4:G502"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Cod"/>
     <x:tableColumn id="2" name="Secc"/>
@@ -245,7 +245,7 @@
     <x:row r="2">
       <x:c r="A2" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Extraído de: HORARIOS 26-2 (2).xlsx</x:t>
+          <x:t xml:space="preserve">Extraído de: HORARIOS 26-2.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" s="2" t="n"/>
@@ -258,7 +258,7 @@
     <x:row r="3">
       <x:c r="A3" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Total de filas extraídas: 484</x:t>
+          <x:t xml:space="preserve">Total de filas extraídas: 498</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -5253,7 +5253,7 @@
       </x:c>
       <x:c r="G138" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIROZ MANTARI, MIGUEL ANTONIO / HUATAQUISPE VASQUEZ, MARGOT</x:t>
+          <x:t xml:space="preserve">QUIROZ MANTARI, MIGUEL ANTONIO</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -5290,7 +5290,7 @@
       </x:c>
       <x:c r="G139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIROZ MANTARI, MIGUEL ANTONIO / HUATAQUISPE VASQUEZ, MARGOT</x:t>
+          <x:t xml:space="preserve">QUIROZ MANTARI, MIGUEL ANTONIO</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -8657,7 +8657,7 @@
       </x:c>
       <x:c r="G230" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MONTALVO YSABEL</x:t>
+          <x:t xml:space="preserve">VILLENA JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -8694,7 +8694,7 @@
       </x:c>
       <x:c r="G231" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MONTALVO YSABEL</x:t>
+          <x:t xml:space="preserve">VILLENA JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -8758,7 +8758,7 @@
       </x:c>
       <x:c r="E233" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 11-14</x:t>
+          <x:t xml:space="preserve">MI 18-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F233" s="7" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </x:c>
       <x:c r="E258" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 18-20</x:t>
+          <x:t xml:space="preserve">MA 18-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F258" s="7" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </x:c>
       <x:c r="E259" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 17-20</x:t>
+          <x:t xml:space="preserve">VI 17-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F259" s="7" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </x:c>
       <x:c r="G259" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AYALA CHRISTIAN</x:t>
+          <x:t xml:space="preserve">NORES LUIS</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10053,7 +10053,7 @@
       </x:c>
       <x:c r="E268" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 18-20</x:t>
+          <x:t xml:space="preserve">VI 15-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F268" s="7" t="inlineStr">
@@ -10403,7 +10403,7 @@
     <x:row r="278">
       <x:c r="A278" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA626</x:t>
+          <x:t xml:space="preserve">SA654</x:t>
         </x:is>
       </x:c>
       <x:c r="B278" s="6" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </x:c>
       <x:c r="C278" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ventilación Industrial II</x:t>
+          <x:t xml:space="preserve">Ergonomía</x:t>
         </x:is>
       </x:c>
       <x:c r="D278" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E278" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 18-20</x:t>
+          <x:t xml:space="preserve">VI 16-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F278" s="7" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </x:c>
       <x:c r="G278" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JUAN NARCISO</x:t>
+          <x:t xml:space="preserve">ULLILEN CAROLINA</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10455,12 +10455,12 @@
       </x:c>
       <x:c r="D279" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E279" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 16-19</x:t>
+          <x:t xml:space="preserve">MA 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F279" s="7" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </x:c>
       <x:c r="C287" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN V EN INGENIERIA DE HIGIENE Y SEGURIDAD INDUSTRIAL</x:t>
+          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D287" s="6" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </x:c>
       <x:c r="E287" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 18-20</x:t>
+          <x:t xml:space="preserve">SA 09-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F287" s="7" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </x:c>
       <x:c r="G287" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BECERRA AMPARO</x:t>
+          <x:t xml:space="preserve">KIKO ALEXI</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10783,7 +10783,7 @@
       </x:c>
       <x:c r="C288" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN V EN INGENIERIA DE HIGIENE Y SEGURIDAD INDUSTRIAL</x:t>
+          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D288" s="6" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </x:c>
       <x:c r="E288" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 18-20</x:t>
+          <x:t xml:space="preserve">SA 09-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F288" s="7" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </x:c>
       <x:c r="G288" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BECERRA AMPARO</x:t>
+          <x:t xml:space="preserve">KIKO ALEXI</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10820,7 +10820,7 @@
       </x:c>
       <x:c r="C289" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN V EN INGENIERIA DE HIGIENE Y SEGURIDAD INDUSTRIAL</x:t>
+          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D289" s="6" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </x:c>
       <x:c r="E289" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 17-19</x:t>
+          <x:t xml:space="preserve">SA 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F289" s="7" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </x:c>
       <x:c r="G289" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BECERRA AMPARO</x:t>
+          <x:t xml:space="preserve">GIL SANDOVAL</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10857,7 +10857,7 @@
       </x:c>
       <x:c r="C290" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN V EN INGENIERIA DE HIGIENE Y SEGURIDAD INDUSTRIAL</x:t>
+          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D290" s="6" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </x:c>
       <x:c r="E290" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 17-19</x:t>
+          <x:t xml:space="preserve">SA 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F290" s="7" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </x:c>
       <x:c r="G290" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BECERRA AMPARO</x:t>
+          <x:t xml:space="preserve">GIL SANDOVAL</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10978,7 +10978,7 @@
       </x:c>
       <x:c r="E293" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 20-22</x:t>
+          <x:t xml:space="preserve">LU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F293" s="7" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </x:c>
       <x:c r="E294" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 17-20</x:t>
+          <x:t xml:space="preserve">MI 16-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F294" s="7" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </x:c>
       <x:c r="E297" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 08-10</x:t>
+          <x:t xml:space="preserve">LU 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F297" s="7" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </x:c>
       <x:c r="E298" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 10-13</x:t>
+          <x:t xml:space="preserve">VI 19-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F298" s="7" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </x:c>
       <x:c r="E299" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 16-18</x:t>
+          <x:t xml:space="preserve">MI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F299" s="7" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </x:c>
       <x:c r="G303" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DELGADO KIKO</x:t>
+          <x:t xml:space="preserve">ROSA AMPARO</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -11385,7 +11385,7 @@
       </x:c>
       <x:c r="E304" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 20-22</x:t>
+          <x:t xml:space="preserve">VI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F304" s="7" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </x:c>
       <x:c r="G304" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DELGADO KIKO</x:t>
+          <x:t xml:space="preserve">ROSA AMPARO</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -11533,7 +11533,7 @@
       </x:c>
       <x:c r="E308" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 20-22</x:t>
+          <x:t xml:space="preserve">MA 19-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F308" s="7" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </x:c>
       <x:c r="G308" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARTINEZ FLORIPEZ</x:t>
+          <x:t xml:space="preserve">NORES ROMERO</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -11698,7 +11698,7 @@
     <x:row r="313">
       <x:c r="A313" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SP110</x:t>
+          <x:t xml:space="preserve">SO321</x:t>
         </x:is>
       </x:c>
       <x:c r="B313" s="6" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </x:c>
       <x:c r="C313" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SALUD PÚBLICA</x:t>
+          <x:t xml:space="preserve">EPIDEMIOLOGÍA DEL TRABAJO</x:t>
         </x:is>
       </x:c>
       <x:c r="D313" s="6" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </x:c>
       <x:c r="E313" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 17-18</x:t>
+          <x:t xml:space="preserve">MA 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F313" s="7" t="inlineStr">
@@ -11728,14 +11728,14 @@
       </x:c>
       <x:c r="G313" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CARRASCO CRISTIAN</x:t>
+          <x:t xml:space="preserve">CAMPOS FLORIPEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SP110</x:t>
+          <x:t xml:space="preserve">SO321</x:t>
         </x:is>
       </x:c>
       <x:c r="B314" s="6" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </x:c>
       <x:c r="C314" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SALUD PÚBLICA</x:t>
+          <x:t xml:space="preserve">EPIDEMIOLOGÍA DEL TRABAJO</x:t>
         </x:is>
       </x:c>
       <x:c r="D314" s="6" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </x:c>
       <x:c r="E314" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 18-20</x:t>
+          <x:t xml:space="preserve">VI 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F314" s="7" t="inlineStr">
@@ -11765,14 +11765,14 @@
       </x:c>
       <x:c r="G314" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CARRASCO CRISTIAN</x:t>
+          <x:t xml:space="preserve">CAMPOS FLORIPEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA140AS870</x:t>
+          <x:t xml:space="preserve">SP110</x:t>
         </x:is>
       </x:c>
       <x:c r="B315" s="6" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </x:c>
       <x:c r="C315" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN EMPRESARIAL</x:t>
+          <x:t xml:space="preserve">SALUD PÚBLICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D315" s="6" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </x:c>
       <x:c r="E315" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-16</x:t>
+          <x:t xml:space="preserve">MI 17-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F315" s="7" t="inlineStr">
@@ -11802,14 +11802,14 @@
       </x:c>
       <x:c r="G315" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALDIVIA PEDRO</x:t>
+          <x:t xml:space="preserve">CARRASCO CRISTIAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA140AS870</x:t>
+          <x:t xml:space="preserve">SP110</x:t>
         </x:is>
       </x:c>
       <x:c r="B316" s="6" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </x:c>
       <x:c r="C316" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN EMPRESARIAL</x:t>
+          <x:t xml:space="preserve">SALUD PÚBLICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D316" s="6" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </x:c>
       <x:c r="E316" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 14-16</x:t>
+          <x:t xml:space="preserve">MI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F316" s="7" t="inlineStr">
@@ -11839,14 +11839,14 @@
       </x:c>
       <x:c r="G316" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALDIVIA PEDRO</x:t>
+          <x:t xml:space="preserve">CARRASCO CRISTIAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SE222</x:t>
+          <x:t xml:space="preserve">SE103</x:t>
         </x:is>
       </x:c>
       <x:c r="B317" s="6" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </x:c>
       <x:c r="C317" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Seguridad e higiene en actividades de pesquería</x:t>
+          <x:t xml:space="preserve">SEGURIDAD E HIGIENE EN CONSTRUCCION</x:t>
         </x:is>
       </x:c>
       <x:c r="D317" s="6" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </x:c>
       <x:c r="E317" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-16</x:t>
+          <x:t xml:space="preserve">VI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F317" s="7" t="inlineStr">
@@ -11876,14 +11876,14 @@
       </x:c>
       <x:c r="G317" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROBLES EUSEBIO</x:t>
+          <x:t xml:space="preserve">MONTALVO FIGUEROA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SE222</x:t>
+          <x:t xml:space="preserve">SE103</x:t>
         </x:is>
       </x:c>
       <x:c r="B318" s="6" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </x:c>
       <x:c r="C318" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Seguridad e higiene en actividades de pesquería</x:t>
+          <x:t xml:space="preserve">SEGURIDAD E HIGIENE EN CONSTRUCCION</x:t>
         </x:is>
       </x:c>
       <x:c r="D318" s="6" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </x:c>
       <x:c r="E318" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 14-16</x:t>
+          <x:t xml:space="preserve">SA 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F318" s="7" t="inlineStr">
@@ -11913,14 +11913,14 @@
       </x:c>
       <x:c r="G318" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROBLES EUSEBIO</x:t>
+          <x:t xml:space="preserve">MONTALVO FIGUEROA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GI120</x:t>
+          <x:t xml:space="preserve">SE222</x:t>
         </x:is>
       </x:c>
       <x:c r="B319" s="6" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </x:c>
       <x:c r="C319" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN ECONÓMICO-FINANCIERA</x:t>
+          <x:t xml:space="preserve">Seguridad e higiene en actividades de pesquería</x:t>
         </x:is>
       </x:c>
       <x:c r="D319" s="6" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </x:c>
       <x:c r="E319" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 13-14</x:t>
+          <x:t xml:space="preserve">LU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F319" s="7" t="inlineStr">
@@ -11950,14 +11950,14 @@
       </x:c>
       <x:c r="G319" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLASOS JORGE</x:t>
+          <x:t xml:space="preserve">ROBLES EUSEBIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GI120</x:t>
+          <x:t xml:space="preserve">SE222</x:t>
         </x:is>
       </x:c>
       <x:c r="B320" s="6" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </x:c>
       <x:c r="C320" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN ECONÓMICO-FINANCIERA</x:t>
+          <x:t xml:space="preserve">Seguridad e higiene en actividades de pesquería</x:t>
         </x:is>
       </x:c>
       <x:c r="D320" s="6" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </x:c>
       <x:c r="E320" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 14-16</x:t>
+          <x:t xml:space="preserve">JU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F320" s="7" t="inlineStr">
@@ -11987,24 +11987,24 @@
       </x:c>
       <x:c r="G320" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLASOS JORGE</x:t>
+          <x:t xml:space="preserve">ROBLES EUSEBIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AHK15</x:t>
+          <x:t xml:space="preserve">AA235</x:t>
         </x:is>
       </x:c>
       <x:c r="B321" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">F</x:t>
+          <x:t xml:space="preserve">E</x:t>
         </x:is>
       </x:c>
       <x:c r="C321" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACION</x:t>
+          <x:t xml:space="preserve">TOPOGRAFÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D321" s="6" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </x:c>
       <x:c r="E321" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 13-14</x:t>
+          <x:t xml:space="preserve">MI 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F321" s="7" t="inlineStr">
@@ -12024,24 +12024,24 @@
       </x:c>
       <x:c r="G321" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CARRILLO JAIME</x:t>
+          <x:t xml:space="preserve">CACERES PEREZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AHK15</x:t>
+          <x:t xml:space="preserve">AA235</x:t>
         </x:is>
       </x:c>
       <x:c r="B322" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">F</x:t>
+          <x:t xml:space="preserve">E</x:t>
         </x:is>
       </x:c>
       <x:c r="C322" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACION</x:t>
+          <x:t xml:space="preserve">TOPOGRAFÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D322" s="6" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </x:c>
       <x:c r="E322" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 14-17</x:t>
+          <x:t xml:space="preserve">VI 14-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F322" s="7" t="inlineStr">
@@ -12061,24 +12061,24 @@
       </x:c>
       <x:c r="G322" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CARRILLO JAIME</x:t>
+          <x:t xml:space="preserve">VILLAVICENCIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH512</x:t>
+          <x:t xml:space="preserve">GA162</x:t>
         </x:is>
       </x:c>
       <x:c r="B323" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C323" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">METEOROLOGIA Y CLIMATOLOGIA</x:t>
+          <x:t xml:space="preserve">SISTEMAS INTEGRADOS DE GESTIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D323" s="6" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </x:c>
       <x:c r="E323" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 16-18</x:t>
+          <x:t xml:space="preserve">LU 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F323" s="7" t="inlineStr">
@@ -12098,24 +12098,24 @@
       </x:c>
       <x:c r="G323" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+          <x:t xml:space="preserve">NORES ROMERO, LUIS ALBERTO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH512</x:t>
+          <x:t xml:space="preserve">GA162</x:t>
         </x:is>
       </x:c>
       <x:c r="B324" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C324" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">METEOROLOGIA Y CLIMATOLOGIA</x:t>
+          <x:t xml:space="preserve">SISTEMAS INTEGRADOS DE GESTIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D324" s="6" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </x:c>
       <x:c r="E324" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 18-20</x:t>
+          <x:t xml:space="preserve">LU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F324" s="7" t="inlineStr">
@@ -12135,14 +12135,14 @@
       </x:c>
       <x:c r="G324" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+          <x:t xml:space="preserve">NORES ROMERO, LUIS ALBERTO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AHD85</x:t>
+          <x:t xml:space="preserve">AHK15</x:t>
         </x:is>
       </x:c>
       <x:c r="B325" s="6" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </x:c>
       <x:c r="C325" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INFORMES TECNICOS</x:t>
+          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACION</x:t>
         </x:is>
       </x:c>
       <x:c r="D325" s="6" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </x:c>
       <x:c r="E325" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 14-15</x:t>
+          <x:t xml:space="preserve">MI 13-14</x:t>
         </x:is>
       </x:c>
       <x:c r="F325" s="7" t="inlineStr">
@@ -12172,14 +12172,14 @@
       </x:c>
       <x:c r="G325" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BRINGAS CIRA</x:t>
+          <x:t xml:space="preserve">CARRILLO JAIME</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AHD85</x:t>
+          <x:t xml:space="preserve">AHK15</x:t>
         </x:is>
       </x:c>
       <x:c r="B326" s="6" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </x:c>
       <x:c r="C326" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INFORMES TECNICOS</x:t>
+          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACION</x:t>
         </x:is>
       </x:c>
       <x:c r="D326" s="6" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </x:c>
       <x:c r="E326" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 15-17</x:t>
+          <x:t xml:space="preserve">MI 14-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F326" s="7" t="inlineStr">
@@ -12209,14 +12209,14 @@
       </x:c>
       <x:c r="G326" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BRINGAS CIRA</x:t>
+          <x:t xml:space="preserve">CARRILLO JAIME</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA158</x:t>
+          <x:t xml:space="preserve">HH512</x:t>
         </x:is>
       </x:c>
       <x:c r="B327" s="6" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </x:c>
       <x:c r="C327" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SIMULACION Y MODELAMIENTO AMBIENTAL</x:t>
+          <x:t xml:space="preserve">METEOROLOGIA Y CLIMATOLOGIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D327" s="6" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </x:c>
       <x:c r="E327" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 08-10</x:t>
+          <x:t xml:space="preserve">VI 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F327" s="7" t="inlineStr">
@@ -12246,14 +12246,14 @@
       </x:c>
       <x:c r="G327" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PINCHE LAURRE, CRISTÓBAL</x:t>
+          <x:t xml:space="preserve">MATOS LIDIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA158</x:t>
+          <x:t xml:space="preserve">HH512</x:t>
         </x:is>
       </x:c>
       <x:c r="B328" s="6" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </x:c>
       <x:c r="C328" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SIMULACION Y MODELAMIENTO AMBIENTAL</x:t>
+          <x:t xml:space="preserve">METEOROLOGIA Y CLIMATOLOGIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D328" s="6" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </x:c>
       <x:c r="E328" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 10-12</x:t>
+          <x:t xml:space="preserve">VI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F328" s="7" t="inlineStr">
@@ -12283,24 +12283,24 @@
       </x:c>
       <x:c r="G328" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PINCHE LAURRE, CRISTÓBAL</x:t>
+          <x:t xml:space="preserve">MATOS LIDIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE133</x:t>
+          <x:t xml:space="preserve">GI120</x:t>
         </x:is>
       </x:c>
       <x:c r="B329" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C329" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTROL DE DESERTIFICACION</x:t>
+          <x:t xml:space="preserve">GESTIÓN ECONÓMICO - FINANCIERA</x:t>
         </x:is>
       </x:c>
       <x:c r="D329" s="6" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </x:c>
       <x:c r="E329" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 09-11</x:t>
+          <x:t xml:space="preserve">SA 13-14</x:t>
         </x:is>
       </x:c>
       <x:c r="F329" s="7" t="inlineStr">
@@ -12320,24 +12320,24 @@
       </x:c>
       <x:c r="G329" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUISPE OJEDA</x:t>
+          <x:t xml:space="preserve">COLLAZOS BELTRÁN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE133</x:t>
+          <x:t xml:space="preserve">GI120</x:t>
         </x:is>
       </x:c>
       <x:c r="B330" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C330" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTROL DE DESERTIFICACION</x:t>
+          <x:t xml:space="preserve">GESTIÓN ECONÓMICO - FINANCIERA</x:t>
         </x:is>
       </x:c>
       <x:c r="D330" s="6" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </x:c>
       <x:c r="E330" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 11-13</x:t>
+          <x:t xml:space="preserve">SA 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F330" s="7" t="inlineStr">
@@ -12357,24 +12357,24 @@
       </x:c>
       <x:c r="G330" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUISPE OJEDA</x:t>
+          <x:t xml:space="preserve">COLLAZOS BELTRÁN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HO150</x:t>
+          <x:t xml:space="preserve">AHD85</x:t>
         </x:is>
       </x:c>
       <x:c r="B331" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C331" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INT. A LA INGENIERIA AMB.</x:t>
+          <x:t xml:space="preserve">INFORMES TECNICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D331" s="6" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </x:c>
       <x:c r="E331" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 09-10</x:t>
+          <x:t xml:space="preserve">VI 14-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F331" s="7" t="inlineStr">
@@ -12394,24 +12394,24 @@
       </x:c>
       <x:c r="G331" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA GIANINNA</x:t>
+          <x:t xml:space="preserve">BRINGAS CIRA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HO150</x:t>
+          <x:t xml:space="preserve">AHD85</x:t>
         </x:is>
       </x:c>
       <x:c r="B332" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C332" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INT. A LA INGENIERIA AMB.</x:t>
+          <x:t xml:space="preserve">INFORMES TECNICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D332" s="6" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </x:c>
       <x:c r="E332" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 10-11</x:t>
+          <x:t xml:space="preserve">VI 15-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F332" s="7" t="inlineStr">
@@ -12431,14 +12431,14 @@
       </x:c>
       <x:c r="G332" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA GIANINNA</x:t>
+          <x:t xml:space="preserve">BRINGAS CIRA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HO150</x:t>
+          <x:t xml:space="preserve">GA142</x:t>
         </x:is>
       </x:c>
       <x:c r="B333" s="6" t="inlineStr">
@@ -12448,17 +12448,17 @@
       </x:c>
       <x:c r="C333" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INT. A LA INGENIERIA AMB.</x:t>
+          <x:t xml:space="preserve">ECOEFICIENCIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D333" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E333" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 11-13</x:t>
+          <x:t xml:space="preserve">SA 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F333" s="7" t="inlineStr">
@@ -12468,14 +12468,14 @@
       </x:c>
       <x:c r="G333" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA GIANINNA</x:t>
+          <x:t xml:space="preserve">ARANA OCHOA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIC01</x:t>
+          <x:t xml:space="preserve">GA142</x:t>
         </x:is>
       </x:c>
       <x:c r="B334" s="6" t="inlineStr">
@@ -12485,17 +12485,17 @@
       </x:c>
       <x:c r="C334" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
+          <x:t xml:space="preserve">ECOEFICIENCIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D334" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E334" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-15</x:t>
+          <x:t xml:space="preserve">SA 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F334" s="7" t="inlineStr">
@@ -12505,34 +12505,34 @@
       </x:c>
       <x:c r="G334" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
+          <x:t xml:space="preserve">ARANA OCHOA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIC01</x:t>
+          <x:t xml:space="preserve">SA312</x:t>
         </x:is>
       </x:c>
       <x:c r="B335" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">E</x:t>
         </x:is>
       </x:c>
       <x:c r="C335" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
+          <x:t xml:space="preserve">ECOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D335" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E335" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 15-17</x:t>
+          <x:t xml:space="preserve">JU 19-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F335" s="7" t="inlineStr">
@@ -12542,34 +12542,34 @@
       </x:c>
       <x:c r="G335" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
+          <x:t xml:space="preserve">HUARACA QUISPE, LIDIA PRISILA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIC01</x:t>
+          <x:t xml:space="preserve">SA312</x:t>
         </x:is>
       </x:c>
       <x:c r="B336" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">H</x:t>
+          <x:t xml:space="preserve">E</x:t>
         </x:is>
       </x:c>
       <x:c r="C336" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
+          <x:t xml:space="preserve">ECOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D336" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E336" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 14-16</x:t>
+          <x:t xml:space="preserve">JU 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F336" s="7" t="inlineStr">
@@ -12579,34 +12579,34 @@
       </x:c>
       <x:c r="G336" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
+          <x:t xml:space="preserve">HUARACA QUISPE, LIDIA PRISILA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIC01</x:t>
+          <x:t xml:space="preserve">GA158</x:t>
         </x:is>
       </x:c>
       <x:c r="B337" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">H</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C337" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
+          <x:t xml:space="preserve">SIMULACION Y MODELAMIENTO AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D337" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E337" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 15-17</x:t>
+          <x:t xml:space="preserve">SA 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F337" s="7" t="inlineStr">
@@ -12616,14 +12616,14 @@
       </x:c>
       <x:c r="G337" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
+          <x:t xml:space="preserve">PINCHE LAURRE, CRISTÓBAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BQU01</x:t>
+          <x:t xml:space="preserve">GA158</x:t>
         </x:is>
       </x:c>
       <x:c r="B338" s="6" t="inlineStr">
@@ -12633,17 +12633,17 @@
       </x:c>
       <x:c r="C338" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIMICA I</x:t>
+          <x:t xml:space="preserve">SIMULACION Y MODELAMIENTO AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D338" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E338" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 11-13</x:t>
+          <x:t xml:space="preserve">SA 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F338" s="7" t="inlineStr">
@@ -12653,14 +12653,14 @@
       </x:c>
       <x:c r="G338" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MASGO CESAR</x:t>
+          <x:t xml:space="preserve">PINCHE LAURRE, CRISTÓBAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BQU01</x:t>
+          <x:t xml:space="preserve">GE133</x:t>
         </x:is>
       </x:c>
       <x:c r="B339" s="6" t="inlineStr">
@@ -12670,17 +12670,17 @@
       </x:c>
       <x:c r="C339" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIMICA I</x:t>
+          <x:t xml:space="preserve">CONTROL DE DESERTIFICACION</x:t>
         </x:is>
       </x:c>
       <x:c r="D339" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E339" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 08-10</x:t>
+          <x:t xml:space="preserve">VI 09-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F339" s="7" t="inlineStr">
@@ -12690,34 +12690,34 @@
       </x:c>
       <x:c r="G339" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">YUPANQUI BILMA</x:t>
+          <x:t xml:space="preserve">QUISPE OJEDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BQU01</x:t>
+          <x:t xml:space="preserve">GE133</x:t>
         </x:is>
       </x:c>
       <x:c r="B340" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">J</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C340" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIMICA I</x:t>
+          <x:t xml:space="preserve">CONTROL DE DESERTIFICACION</x:t>
         </x:is>
       </x:c>
       <x:c r="D340" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E340" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 14-16</x:t>
+          <x:t xml:space="preserve">VI 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F340" s="7" t="inlineStr">
@@ -12727,34 +12727,34 @@
       </x:c>
       <x:c r="G340" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MASGO CESAR</x:t>
+          <x:t xml:space="preserve">QUISPE OJEDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BQU01</x:t>
+          <x:t xml:space="preserve">AA293</x:t>
         </x:is>
       </x:c>
       <x:c r="B341" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">J</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C341" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIMICA I</x:t>
+          <x:t xml:space="preserve">INFERENCIA ESTADISTICA PARA LA INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D341" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E341" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 08-10</x:t>
+          <x:t xml:space="preserve">SA 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F341" s="7" t="inlineStr">
@@ -12764,34 +12764,34 @@
       </x:c>
       <x:c r="G341" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">YUPANQUI BILMA</x:t>
+          <x:t xml:space="preserve">GIL SANDOVAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA01</x:t>
+          <x:t xml:space="preserve">AA293</x:t>
         </x:is>
       </x:c>
       <x:c r="B342" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">F</x:t>
         </x:is>
       </x:c>
       <x:c r="C342" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
+          <x:t xml:space="preserve">INFERENCIA ESTADISTICA PARA LA INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D342" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E342" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 10-12</x:t>
+          <x:t xml:space="preserve">SA 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F342" s="7" t="inlineStr">
@@ -12801,14 +12801,14 @@
       </x:c>
       <x:c r="G342" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
+          <x:t xml:space="preserve">GIL SANDOVAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA01</x:t>
+          <x:t xml:space="preserve">GE132</x:t>
         </x:is>
       </x:c>
       <x:c r="B343" s="6" t="inlineStr">
@@ -12818,17 +12818,17 @@
       </x:c>
       <x:c r="C343" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
+          <x:t xml:space="preserve">CAMBIO CLIMÁTICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D343" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E343" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 08-10</x:t>
+          <x:t xml:space="preserve">LU 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F343" s="7" t="inlineStr">
@@ -12838,14 +12838,14 @@
       </x:c>
       <x:c r="G343" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
+          <x:t xml:space="preserve">GIL SANDOVAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA01</x:t>
+          <x:t xml:space="preserve">GE132</x:t>
         </x:is>
       </x:c>
       <x:c r="B344" s="6" t="inlineStr">
@@ -12855,17 +12855,17 @@
       </x:c>
       <x:c r="C344" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
+          <x:t xml:space="preserve">CAMBIO CLIMÁTICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D344" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E344" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 10-12</x:t>
+          <x:t xml:space="preserve">LU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F344" s="7" t="inlineStr">
@@ -12875,24 +12875,24 @@
       </x:c>
       <x:c r="G344" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
+          <x:t xml:space="preserve">GIL SANDOVAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA01</x:t>
+          <x:t xml:space="preserve">HO150</x:t>
         </x:is>
       </x:c>
       <x:c r="B345" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">J</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C345" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
+          <x:t xml:space="preserve">INT. A LA INGENIERIA AMB.</x:t>
         </x:is>
       </x:c>
       <x:c r="D345" s="6" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </x:c>
       <x:c r="E345" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 13-15</x:t>
+          <x:t xml:space="preserve">LU 09-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F345" s="7" t="inlineStr">
@@ -12912,34 +12912,34 @@
       </x:c>
       <x:c r="G345" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
+          <x:t xml:space="preserve">ARANA GIANINNA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA01</x:t>
+          <x:t xml:space="preserve">HO150</x:t>
         </x:is>
       </x:c>
       <x:c r="B346" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">J</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C346" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
+          <x:t xml:space="preserve">INT. A LA INGENIERIA AMB.</x:t>
         </x:is>
       </x:c>
       <x:c r="D346" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E346" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 15-17</x:t>
+          <x:t xml:space="preserve">LU 10-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F346" s="7" t="inlineStr">
@@ -12949,24 +12949,24 @@
       </x:c>
       <x:c r="G346" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
+          <x:t xml:space="preserve">ARANA GIANINNA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA01</x:t>
+          <x:t xml:space="preserve">HO150</x:t>
         </x:is>
       </x:c>
       <x:c r="B347" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">J</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C347" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
+          <x:t xml:space="preserve">INT. A LA INGENIERIA AMB.</x:t>
         </x:is>
       </x:c>
       <x:c r="D347" s="6" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </x:c>
       <x:c r="E347" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 08-10</x:t>
+          <x:t xml:space="preserve">VI 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F347" s="7" t="inlineStr">
@@ -12986,14 +12986,14 @@
       </x:c>
       <x:c r="G347" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CABRERA CESAR</x:t>
+          <x:t xml:space="preserve">ARANA GIANINNA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA03</x:t>
+          <x:t xml:space="preserve">BIC01</x:t>
         </x:is>
       </x:c>
       <x:c r="B348" s="6" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </x:c>
       <x:c r="C348" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALGEBRA LINEAL</x:t>
+          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D348" s="6" t="inlineStr">
@@ -13013,7 +13013,7 @@
       </x:c>
       <x:c r="E348" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 08-11</x:t>
+          <x:t xml:space="preserve">LU 14-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F348" s="7" t="inlineStr">
@@ -13023,14 +13023,14 @@
       </x:c>
       <x:c r="G348" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVARADO LUIS</x:t>
+          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA03</x:t>
+          <x:t xml:space="preserve">BIC01</x:t>
         </x:is>
       </x:c>
       <x:c r="B349" s="6" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </x:c>
       <x:c r="C349" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALGEBRA LINEAL</x:t>
+          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D349" s="6" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </x:c>
       <x:c r="E349" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 08-10</x:t>
+          <x:t xml:space="preserve">LU 15-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F349" s="7" t="inlineStr">
@@ -13060,24 +13060,24 @@
       </x:c>
       <x:c r="G349" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVARADO LUIS</x:t>
+          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEF01</x:t>
+          <x:t xml:space="preserve">BIC01</x:t>
         </x:is>
       </x:c>
       <x:c r="B350" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">H</x:t>
         </x:is>
       </x:c>
       <x:c r="C350" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ÉTICA Y FILOSOFÍA POLÍTICA</x:t>
+          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D350" s="6" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </x:c>
       <x:c r="E350" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 15-16</x:t>
+          <x:t xml:space="preserve">MI 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F350" s="7" t="inlineStr">
@@ -13097,24 +13097,24 @@
       </x:c>
       <x:c r="G350" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
+          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEF01</x:t>
+          <x:t xml:space="preserve">BIC01</x:t>
         </x:is>
       </x:c>
       <x:c r="B351" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">H</x:t>
         </x:is>
       </x:c>
       <x:c r="C351" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ÉTICA Y FILOSOFÍA POLÍTICA</x:t>
+          <x:t xml:space="preserve">INTR. A LA COMPUTACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D351" s="6" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </x:c>
       <x:c r="E351" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 16-18</x:t>
+          <x:t xml:space="preserve">MI 15-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F351" s="7" t="inlineStr">
@@ -13134,14 +13134,14 @@
       </x:c>
       <x:c r="G351" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
+          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BRC01</x:t>
+          <x:t xml:space="preserve">BQU01</x:t>
         </x:is>
       </x:c>
       <x:c r="B352" s="6" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </x:c>
       <x:c r="C352" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REDACCIÓN Y COMUNICACIÓN</x:t>
+          <x:t xml:space="preserve">QUIMICA I</x:t>
         </x:is>
       </x:c>
       <x:c r="D352" s="6" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </x:c>
       <x:c r="E352" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 11-12</x:t>
+          <x:t xml:space="preserve">LU 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F352" s="7" t="inlineStr">
@@ -13171,14 +13171,14 @@
       </x:c>
       <x:c r="G352" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
+          <x:t xml:space="preserve">MASGO CESAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BRC01</x:t>
+          <x:t xml:space="preserve">BQU01</x:t>
         </x:is>
       </x:c>
       <x:c r="B353" s="6" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </x:c>
       <x:c r="C353" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REDACCIÓN Y COMUNICACIÓN</x:t>
+          <x:t xml:space="preserve">QUIMICA I</x:t>
         </x:is>
       </x:c>
       <x:c r="D353" s="6" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </x:c>
       <x:c r="E353" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 12-14</x:t>
+          <x:t xml:space="preserve">MI 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F353" s="7" t="inlineStr">
@@ -13208,24 +13208,24 @@
       </x:c>
       <x:c r="G353" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
+          <x:t xml:space="preserve">YUPANQUI BILMA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA301</x:t>
+          <x:t xml:space="preserve">BQU01</x:t>
         </x:is>
       </x:c>
       <x:c r="B354" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">J</x:t>
         </x:is>
       </x:c>
       <x:c r="C354" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIOLOGIA GENERAL</x:t>
+          <x:t xml:space="preserve">QUIMICA I</x:t>
         </x:is>
       </x:c>
       <x:c r="D354" s="6" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </x:c>
       <x:c r="E354" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 08-11</x:t>
+          <x:t xml:space="preserve">JU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F354" s="7" t="inlineStr">
@@ -13245,24 +13245,24 @@
       </x:c>
       <x:c r="G354" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CHAPILLIQUEN JOSE</x:t>
+          <x:t xml:space="preserve">MASGO CESAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA301</x:t>
+          <x:t xml:space="preserve">BQU01</x:t>
         </x:is>
       </x:c>
       <x:c r="B355" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">J</x:t>
         </x:is>
       </x:c>
       <x:c r="C355" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIOLOGIA GENERAL</x:t>
+          <x:t xml:space="preserve">QUIMICA I</x:t>
         </x:is>
       </x:c>
       <x:c r="D355" s="6" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </x:c>
       <x:c r="E355" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 08-11</x:t>
+          <x:t xml:space="preserve">MI 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F355" s="7" t="inlineStr">
@@ -13282,14 +13282,14 @@
       </x:c>
       <x:c r="G355" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CHAPILLIQUEN JOSE</x:t>
+          <x:t xml:space="preserve">YUPANQUI BILMA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA238</x:t>
+          <x:t xml:space="preserve">BMA01</x:t>
         </x:is>
       </x:c>
       <x:c r="B356" s="6" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </x:c>
       <x:c r="C356" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
+          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D356" s="6" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </x:c>
       <x:c r="E356" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 14-15</x:t>
+          <x:t xml:space="preserve">MI 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F356" s="7" t="inlineStr">
@@ -13319,14 +13319,14 @@
       </x:c>
       <x:c r="G356" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
+          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA238</x:t>
+          <x:t xml:space="preserve">BMA01</x:t>
         </x:is>
       </x:c>
       <x:c r="B357" s="6" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </x:c>
       <x:c r="C357" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
+          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D357" s="6" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </x:c>
       <x:c r="E357" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 15-18</x:t>
+          <x:t xml:space="preserve">MA 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F357" s="7" t="inlineStr">
@@ -13356,14 +13356,14 @@
       </x:c>
       <x:c r="G357" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
+          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA238</x:t>
+          <x:t xml:space="preserve">BMA01</x:t>
         </x:is>
       </x:c>
       <x:c r="B358" s="6" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </x:c>
       <x:c r="C358" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
+          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D358" s="6" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </x:c>
       <x:c r="E358" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 16-17</x:t>
+          <x:t xml:space="preserve">JU 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F358" s="7" t="inlineStr">
@@ -13393,34 +13393,34 @@
       </x:c>
       <x:c r="G358" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
+          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA238</x:t>
+          <x:t xml:space="preserve">BMA01</x:t>
         </x:is>
       </x:c>
       <x:c r="B359" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">J</x:t>
         </x:is>
       </x:c>
       <x:c r="C359" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
+          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D359" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E359" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 17-20</x:t>
+          <x:t xml:space="preserve">MI 13-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F359" s="7" t="inlineStr">
@@ -13430,24 +13430,24 @@
       </x:c>
       <x:c r="G359" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
+          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA246</x:t>
+          <x:t xml:space="preserve">BMA01</x:t>
         </x:is>
       </x:c>
       <x:c r="B360" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">J</x:t>
         </x:is>
       </x:c>
       <x:c r="C360" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LENGUAJE DE PROGRAMACION</x:t>
+          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D360" s="6" t="inlineStr">
@@ -13457,7 +13457,7 @@
       </x:c>
       <x:c r="E360" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 12-14</x:t>
+          <x:t xml:space="preserve">JU 15-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F360" s="7" t="inlineStr">
@@ -13467,14 +13467,14 @@
       </x:c>
       <x:c r="G360" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
+          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA246</x:t>
+          <x:t xml:space="preserve">BMA01</x:t>
         </x:is>
       </x:c>
       <x:c r="B361" s="6" t="inlineStr">
@@ -13484,17 +13484,17 @@
       </x:c>
       <x:c r="C361" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LENGUAJE DE PROGRAMACIÓN</x:t>
+          <x:t xml:space="preserve">CÁLCULO DIFERENCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D361" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E361" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 16-18</x:t>
+          <x:t xml:space="preserve">MA 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F361" s="7" t="inlineStr">
@@ -13504,14 +13504,14 @@
       </x:c>
       <x:c r="G361" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
+          <x:t xml:space="preserve">CABRERA CESAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BFI01</x:t>
+          <x:t xml:space="preserve">BMA03</x:t>
         </x:is>
       </x:c>
       <x:c r="B362" s="6" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </x:c>
       <x:c r="C362" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICA I</x:t>
+          <x:t xml:space="preserve">ALGEBRA LINEAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D362" s="6" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </x:c>
       <x:c r="E362" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 17-19</x:t>
+          <x:t xml:space="preserve">VI 08-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F362" s="7" t="inlineStr">
@@ -13541,14 +13541,14 @@
       </x:c>
       <x:c r="G362" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MENDOZA DAYGORD</x:t>
+          <x:t xml:space="preserve">ALVARADO LUIS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BFI01</x:t>
+          <x:t xml:space="preserve">BMA03</x:t>
         </x:is>
       </x:c>
       <x:c r="B363" s="6" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </x:c>
       <x:c r="C363" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICA I</x:t>
+          <x:t xml:space="preserve">ALGEBRA LINEAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D363" s="6" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </x:c>
       <x:c r="E363" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 15-18</x:t>
+          <x:t xml:space="preserve">JU 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F363" s="7" t="inlineStr">
@@ -13578,14 +13578,14 @@
       </x:c>
       <x:c r="G363" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MENDOZA DAYGORD</x:t>
+          <x:t xml:space="preserve">ALVARADO LUIS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BFI01</x:t>
+          <x:t xml:space="preserve">BEF01</x:t>
         </x:is>
       </x:c>
       <x:c r="B364" s="6" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </x:c>
       <x:c r="C364" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICA I</x:t>
+          <x:t xml:space="preserve">ÉTICA Y FILOSOFÍA POLÍTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D364" s="6" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </x:c>
       <x:c r="E364" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 11-13</x:t>
+          <x:t xml:space="preserve">MA 15-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F364" s="7" t="inlineStr">
@@ -13615,14 +13615,14 @@
       </x:c>
       <x:c r="G364" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MENDOZA DAYGORD</x:t>
+          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA223</x:t>
+          <x:t xml:space="preserve">BEF01</x:t>
         </x:is>
       </x:c>
       <x:c r="B365" s="6" t="inlineStr">
@@ -13632,17 +13632,17 @@
       </x:c>
       <x:c r="C365" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIMICA II</x:t>
+          <x:t xml:space="preserve">ÉTICA Y FILOSOFÍA POLÍTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D365" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E365" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 17-19</x:t>
+          <x:t xml:space="preserve">MA 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F365" s="7" t="inlineStr">
@@ -13652,14 +13652,14 @@
       </x:c>
       <x:c r="G365" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GARAY JUAN DE DIOS</x:t>
+          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA223</x:t>
+          <x:t xml:space="preserve">BRC01</x:t>
         </x:is>
       </x:c>
       <x:c r="B366" s="6" t="inlineStr">
@@ -13669,17 +13669,17 @@
       </x:c>
       <x:c r="C366" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIMICA II</x:t>
+          <x:t xml:space="preserve">REDACCIÓN Y COMUNICACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D366" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E366" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 08-10</x:t>
+          <x:t xml:space="preserve">MA 11-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F366" s="7" t="inlineStr">
@@ -13689,14 +13689,14 @@
       </x:c>
       <x:c r="G366" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CARRILLO HERNANDEZ MIGUEL</x:t>
+          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA02</x:t>
+          <x:t xml:space="preserve">BRC01</x:t>
         </x:is>
       </x:c>
       <x:c r="B367" s="6" t="inlineStr">
@@ -13706,17 +13706,17 @@
       </x:c>
       <x:c r="C367" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CALCULO INTEGRAL</x:t>
+          <x:t xml:space="preserve">REDACCIÓN Y COMUNICACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D367" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E367" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 08-10</x:t>
+          <x:t xml:space="preserve">MA 12-14</x:t>
         </x:is>
       </x:c>
       <x:c r="F367" s="7" t="inlineStr">
@@ -13726,14 +13726,14 @@
       </x:c>
       <x:c r="G367" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
+          <x:t xml:space="preserve">GONZALEZ CONSUELO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMA02</x:t>
+          <x:t xml:space="preserve">SA301</x:t>
         </x:is>
       </x:c>
       <x:c r="B368" s="6" t="inlineStr">
@@ -13743,17 +13743,17 @@
       </x:c>
       <x:c r="C368" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CALCULO INTEGRAL</x:t>
+          <x:t xml:space="preserve">BIOLOGIA GENERAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D368" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E368" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 14-16</x:t>
+          <x:t xml:space="preserve">SA 08-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F368" s="7" t="inlineStr">
@@ -13763,14 +13763,14 @@
       </x:c>
       <x:c r="G368" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
+          <x:t xml:space="preserve">CHAPILLIQUEN JOSE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BRN01</x:t>
+          <x:t xml:space="preserve">SA301</x:t>
         </x:is>
       </x:c>
       <x:c r="B369" s="6" t="inlineStr">
@@ -13780,17 +13780,17 @@
       </x:c>
       <x:c r="C369" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REALIDAD NACIONAL, CONSTITUCIÓN</x:t>
+          <x:t xml:space="preserve">BIOLOGIA GENERAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D369" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E369" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 08-10</x:t>
+          <x:t xml:space="preserve">LU 08-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F369" s="7" t="inlineStr">
@@ -13800,14 +13800,14 @@
       </x:c>
       <x:c r="G369" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AUBERT CÁRDENAS RUTH</x:t>
+          <x:t xml:space="preserve">CHAPILLIQUEN JOSE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BRN01</x:t>
+          <x:t xml:space="preserve">AA238</x:t>
         </x:is>
       </x:c>
       <x:c r="B370" s="6" t="inlineStr">
@@ -13817,17 +13817,17 @@
       </x:c>
       <x:c r="C370" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REALIDAD NACIONAL, CONSTITUCIÓN</x:t>
+          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D370" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E370" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 10-12</x:t>
+          <x:t xml:space="preserve">SA 14-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F370" s="7" t="inlineStr">
@@ -13837,14 +13837,14 @@
       </x:c>
       <x:c r="G370" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AUBERT CÁRDENAS RUTH</x:t>
+          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA215</x:t>
+          <x:t xml:space="preserve">AA238</x:t>
         </x:is>
       </x:c>
       <x:c r="B371" s="6" t="inlineStr">
@@ -13854,17 +13854,17 @@
       </x:c>
       <x:c r="C371" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GEOLOGIA</x:t>
+          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D371" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E371" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 16-18</x:t>
+          <x:t xml:space="preserve">SA 15-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F371" s="7" t="inlineStr">
@@ -13874,14 +13874,14 @@
       </x:c>
       <x:c r="G371" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MECHATO ALCAS YMELDA</x:t>
+          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA215</x:t>
+          <x:t xml:space="preserve">AA238</x:t>
         </x:is>
       </x:c>
       <x:c r="B372" s="6" t="inlineStr">
@@ -13891,17 +13891,17 @@
       </x:c>
       <x:c r="C372" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GEOLOGIA</x:t>
+          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D372" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E372" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 18-20</x:t>
+          <x:t xml:space="preserve">MA 16-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F372" s="7" t="inlineStr">
@@ -13911,14 +13911,14 @@
       </x:c>
       <x:c r="G372" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MECHATO ALCAS YMELDA</x:t>
+          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA312</x:t>
+          <x:t xml:space="preserve">AA238</x:t>
         </x:is>
       </x:c>
       <x:c r="B373" s="6" t="inlineStr">
@@ -13928,17 +13928,17 @@
       </x:c>
       <x:c r="C373" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECOLOGÍA</x:t>
+          <x:t xml:space="preserve">DIBUJO CARTOGRÁFICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D373" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E373" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 12-13</x:t>
+          <x:t xml:space="preserve">MA 17-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F373" s="7" t="inlineStr">
@@ -13948,14 +13948,14 @@
       </x:c>
       <x:c r="G373" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HEIDI SANCHEZ</x:t>
+          <x:t xml:space="preserve">AGUILAR JUAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA312</x:t>
+          <x:t xml:space="preserve">AA246</x:t>
         </x:is>
       </x:c>
       <x:c r="B374" s="6" t="inlineStr">
@@ -13965,17 +13965,17 @@
       </x:c>
       <x:c r="C374" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECOLOGÍA</x:t>
+          <x:t xml:space="preserve">LENGUAJE DE PROGRAMACION</x:t>
         </x:is>
       </x:c>
       <x:c r="D374" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E374" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 11-13</x:t>
+          <x:t xml:space="preserve">MI 12-14</x:t>
         </x:is>
       </x:c>
       <x:c r="F374" s="7" t="inlineStr">
@@ -13985,24 +13985,24 @@
       </x:c>
       <x:c r="G374" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HEIDI SANCHEZ</x:t>
+          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA234</x:t>
+          <x:t xml:space="preserve">AA246</x:t>
         </x:is>
       </x:c>
       <x:c r="B375" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">J</x:t>
         </x:is>
       </x:c>
       <x:c r="C375" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICA II</x:t>
+          <x:t xml:space="preserve">LENGUAJE DE PROGRAMACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D375" s="6" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </x:c>
       <x:c r="E375" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 08-11</x:t>
+          <x:t xml:space="preserve">VI 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F375" s="7" t="inlineStr">
@@ -14022,14 +14022,14 @@
       </x:c>
       <x:c r="G375" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ASENCIOS JUNIOR</x:t>
+          <x:t xml:space="preserve">HUAMAN JORGE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA234</x:t>
+          <x:t xml:space="preserve">BFI01</x:t>
         </x:is>
       </x:c>
       <x:c r="B376" s="6" t="inlineStr">
@@ -14039,17 +14039,17 @@
       </x:c>
       <x:c r="C376" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICA II</x:t>
+          <x:t xml:space="preserve">FISICA I</x:t>
         </x:is>
       </x:c>
       <x:c r="D376" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E376" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 08-11</x:t>
+          <x:t xml:space="preserve">MA 17-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F376" s="7" t="inlineStr">
@@ -14059,14 +14059,14 @@
       </x:c>
       <x:c r="G376" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LA ROSA DOMINGO</x:t>
+          <x:t xml:space="preserve">MENDOZA DAYGORD</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA243</x:t>
+          <x:t xml:space="preserve">BFI01</x:t>
         </x:is>
       </x:c>
       <x:c r="B377" s="6" t="inlineStr">
@@ -14076,17 +14076,17 @@
       </x:c>
       <x:c r="C377" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICO QUÍMICA APLICADA</x:t>
+          <x:t xml:space="preserve">FISICA I</x:t>
         </x:is>
       </x:c>
       <x:c r="D377" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E377" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-16</x:t>
+          <x:t xml:space="preserve">LU 15-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F377" s="7" t="inlineStr">
@@ -14096,14 +14096,14 @@
       </x:c>
       <x:c r="G377" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GARAY JUAN</x:t>
+          <x:t xml:space="preserve">MENDOZA DAYGORD</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA243</x:t>
+          <x:t xml:space="preserve">BFI01</x:t>
         </x:is>
       </x:c>
       <x:c r="B378" s="6" t="inlineStr">
@@ -14113,17 +14113,17 @@
       </x:c>
       <x:c r="C378" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICO QUÍMICA APLICADA</x:t>
+          <x:t xml:space="preserve">FISICA I</x:t>
         </x:is>
       </x:c>
       <x:c r="D378" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E378" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 14-17</x:t>
+          <x:t xml:space="preserve">SA 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F378" s="7" t="inlineStr">
@@ -14133,14 +14133,14 @@
       </x:c>
       <x:c r="G378" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GARAY JUAN</x:t>
+          <x:t xml:space="preserve">MENDOZA DAYGORD</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA232</x:t>
+          <x:t xml:space="preserve">AA223</x:t>
         </x:is>
       </x:c>
       <x:c r="B379" s="6" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </x:c>
       <x:c r="C379" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIOESTADISTICA</x:t>
+          <x:t xml:space="preserve">QUIMICA II</x:t>
         </x:is>
       </x:c>
       <x:c r="D379" s="6" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </x:c>
       <x:c r="E379" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 08-11</x:t>
+          <x:t xml:space="preserve">JU 17-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F379" s="7" t="inlineStr">
@@ -14170,14 +14170,14 @@
       </x:c>
       <x:c r="G379" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CASTAÑEDA BEATRIZ</x:t>
+          <x:t xml:space="preserve">GARAY JUAN DE DIOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA232</x:t>
+          <x:t xml:space="preserve">AA223</x:t>
         </x:is>
       </x:c>
       <x:c r="B380" s="6" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </x:c>
       <x:c r="C380" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIOESTADISTICA</x:t>
+          <x:t xml:space="preserve">QUIMICA II</x:t>
         </x:is>
       </x:c>
       <x:c r="D380" s="6" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </x:c>
       <x:c r="E380" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 08-10</x:t>
+          <x:t xml:space="preserve">MA 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F380" s="7" t="inlineStr">
@@ -14207,14 +14207,14 @@
       </x:c>
       <x:c r="G380" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CASTAÑEDA BEATRIZ</x:t>
+          <x:t xml:space="preserve">CARRILLO HERNANDEZ MIGUEL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA241G</x:t>
+          <x:t xml:space="preserve">BMA02</x:t>
         </x:is>
       </x:c>
       <x:c r="B381" s="6" t="inlineStr">
@@ -14224,17 +14224,17 @@
       </x:c>
       <x:c r="C381" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CÁLCULO MULTIVARIABLE</x:t>
+          <x:t xml:space="preserve">CALCULO INTEGRAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D381" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E381" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 14-16</x:t>
+          <x:t xml:space="preserve">MI 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F381" s="7" t="inlineStr">
@@ -14244,14 +14244,14 @@
       </x:c>
       <x:c r="G381" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUILLCA PEDRO</x:t>
+          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEG01</x:t>
+          <x:t xml:space="preserve">BMA02</x:t>
         </x:is>
       </x:c>
       <x:c r="B382" s="6" t="inlineStr">
@@ -14261,17 +14261,17 @@
       </x:c>
       <x:c r="C382" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECONOMIA GENERAL</x:t>
+          <x:t xml:space="preserve">CALCULO INTEGRAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D382" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E382" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 08-10</x:t>
+          <x:t xml:space="preserve">MA 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F382" s="7" t="inlineStr">
@@ -14281,14 +14281,14 @@
       </x:c>
       <x:c r="G382" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AUBERT CÁRDENAS RUTH</x:t>
+          <x:t xml:space="preserve">HERRERA HECTOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEG01</x:t>
+          <x:t xml:space="preserve">BRN01</x:t>
         </x:is>
       </x:c>
       <x:c r="B383" s="6" t="inlineStr">
@@ -14298,17 +14298,17 @@
       </x:c>
       <x:c r="C383" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECONOMIA GENERAL</x:t>
+          <x:t xml:space="preserve">REALIDAD NACIONAL, CONSTITUCIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D383" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E383" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 10-12</x:t>
+          <x:t xml:space="preserve">VI 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F383" s="7" t="inlineStr">
@@ -14325,7 +14325,7 @@
     <x:row r="384">
       <x:c r="A384" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE102</x:t>
+          <x:t xml:space="preserve">BRN01</x:t>
         </x:is>
       </x:c>
       <x:c r="B384" s="6" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </x:c>
       <x:c r="C384" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GEOGRAFÍA</x:t>
+          <x:t xml:space="preserve">REALIDAD NACIONAL, CONSTITUCIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D384" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E384" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-16</x:t>
+          <x:t xml:space="preserve">VI 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F384" s="7" t="inlineStr">
@@ -14355,14 +14355,14 @@
       </x:c>
       <x:c r="G384" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
+          <x:t xml:space="preserve">AUBERT CÁRDENAS RUTH</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE102</x:t>
+          <x:t xml:space="preserve">AA215</x:t>
         </x:is>
       </x:c>
       <x:c r="B385" s="6" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </x:c>
       <x:c r="C385" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GEOGRAFÍA</x:t>
+          <x:t xml:space="preserve">GEOLOGIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D385" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E385" s="6" t="inlineStr">
@@ -14392,14 +14392,14 @@
       </x:c>
       <x:c r="G385" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
+          <x:t xml:space="preserve">MECHATO ALCAS YMELDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QU125</x:t>
+          <x:t xml:space="preserve">AA215</x:t>
         </x:is>
       </x:c>
       <x:c r="B386" s="6" t="inlineStr">
@@ -14409,17 +14409,17 @@
       </x:c>
       <x:c r="C386" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIOQUIMICA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">GEOLOGIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D386" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E386" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 18-20</x:t>
+          <x:t xml:space="preserve">LU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F386" s="7" t="inlineStr">
@@ -14429,14 +14429,14 @@
       </x:c>
       <x:c r="G386" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARIN HUACHACA, NELIDA</x:t>
+          <x:t xml:space="preserve">MECHATO ALCAS YMELDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QU125</x:t>
+          <x:t xml:space="preserve">SA312</x:t>
         </x:is>
       </x:c>
       <x:c r="B387" s="6" t="inlineStr">
@@ -14446,17 +14446,17 @@
       </x:c>
       <x:c r="C387" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIOQUIMICA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">ECOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D387" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E387" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 14-16</x:t>
+          <x:t xml:space="preserve">LU 12-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F387" s="7" t="inlineStr">
@@ -14466,14 +14466,14 @@
       </x:c>
       <x:c r="G387" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARIN HUACHACA, NELIDA</x:t>
+          <x:t xml:space="preserve">HEIDI SANCHEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FI413</x:t>
+          <x:t xml:space="preserve">SA312</x:t>
         </x:is>
       </x:c>
       <x:c r="B388" s="6" t="inlineStr">
@@ -14483,17 +14483,17 @@
       </x:c>
       <x:c r="C388" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICA III</x:t>
+          <x:t xml:space="preserve">ECOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D388" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E388" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 14-16</x:t>
+          <x:t xml:space="preserve">MA 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F388" s="7" t="inlineStr">
@@ -14503,14 +14503,14 @@
       </x:c>
       <x:c r="G388" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARAS OSCAR</x:t>
+          <x:t xml:space="preserve">HEIDI SANCHEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FI413</x:t>
+          <x:t xml:space="preserve">AA234</x:t>
         </x:is>
       </x:c>
       <x:c r="B389" s="6" t="inlineStr">
@@ -14520,17 +14520,17 @@
       </x:c>
       <x:c r="C389" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISICA III</x:t>
+          <x:t xml:space="preserve">FISICA II</x:t>
         </x:is>
       </x:c>
       <x:c r="D389" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E389" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 14-17</x:t>
+          <x:t xml:space="preserve">SA 08-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F389" s="7" t="inlineStr">
@@ -14540,14 +14540,14 @@
       </x:c>
       <x:c r="G389" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARAS OSCAR</x:t>
+          <x:t xml:space="preserve">ASENCIOS JUNIOR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA425</x:t>
+          <x:t xml:space="preserve">AA234</x:t>
         </x:is>
       </x:c>
       <x:c r="B390" s="6" t="inlineStr">
@@ -14557,17 +14557,17 @@
       </x:c>
       <x:c r="C390" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DISEÑO Y EVALUACION DE PROYECTOS</x:t>
+          <x:t xml:space="preserve">FISICA II</x:t>
         </x:is>
       </x:c>
       <x:c r="D390" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E390" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 10-13</x:t>
+          <x:t xml:space="preserve">MA 08-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F390" s="7" t="inlineStr">
@@ -14577,14 +14577,14 @@
       </x:c>
       <x:c r="G390" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
+          <x:t xml:space="preserve">LA ROSA DOMINGO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA425</x:t>
+          <x:t xml:space="preserve">AA243</x:t>
         </x:is>
       </x:c>
       <x:c r="B391" s="6" t="inlineStr">
@@ -14594,17 +14594,17 @@
       </x:c>
       <x:c r="C391" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DISEÑO Y EVALUACION DE PROYECTOS</x:t>
+          <x:t xml:space="preserve">FISICO QUÍMICA APLICADA</x:t>
         </x:is>
       </x:c>
       <x:c r="D391" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E391" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 11-12</x:t>
+          <x:t xml:space="preserve">LU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F391" s="7" t="inlineStr">
@@ -14614,14 +14614,14 @@
       </x:c>
       <x:c r="G391" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
+          <x:t xml:space="preserve">GARAY JUAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA153</x:t>
+          <x:t xml:space="preserve">AA243</x:t>
         </x:is>
       </x:c>
       <x:c r="B392" s="6" t="inlineStr">
@@ -14631,17 +14631,17 @@
       </x:c>
       <x:c r="C392" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECUACIONES DIFERENCIALES</x:t>
+          <x:t xml:space="preserve">FISICO QUÍMICA APLICADA</x:t>
         </x:is>
       </x:c>
       <x:c r="D392" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E392" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 08-11</x:t>
+          <x:t xml:space="preserve">MI 14-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F392" s="7" t="inlineStr">
@@ -14651,14 +14651,14 @@
       </x:c>
       <x:c r="G392" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUILLCA PEDRO</x:t>
+          <x:t xml:space="preserve">GARAY JUAN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA153</x:t>
+          <x:t xml:space="preserve">AA232</x:t>
         </x:is>
       </x:c>
       <x:c r="B393" s="6" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </x:c>
       <x:c r="C393" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECUACIONES DIFERENCIALES</x:t>
+          <x:t xml:space="preserve">BIOESTADISTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D393" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E393" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 10-12</x:t>
+          <x:t xml:space="preserve">JU 08-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F393" s="7" t="inlineStr">
@@ -14688,14 +14688,14 @@
       </x:c>
       <x:c r="G393" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HUILLCA PEDRO</x:t>
+          <x:t xml:space="preserve">CASTAÑEDA BEATRIZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS163</x:t>
+          <x:t xml:space="preserve">AA232</x:t>
         </x:is>
       </x:c>
       <x:c r="B394" s="6" t="inlineStr">
@@ -14705,17 +14705,17 @@
       </x:c>
       <x:c r="C394" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SOCIOLOGÍA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">BIOESTADISTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D394" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E394" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 09-10</x:t>
+          <x:t xml:space="preserve">MI 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F394" s="7" t="inlineStr">
@@ -14725,14 +14725,14 @@
       </x:c>
       <x:c r="G394" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARUJA RIVAS</x:t>
+          <x:t xml:space="preserve">CASTAÑEDA BEATRIZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS163</x:t>
+          <x:t xml:space="preserve">AA241G</x:t>
         </x:is>
       </x:c>
       <x:c r="B395" s="6" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </x:c>
       <x:c r="C395" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SOCIOLOGÍA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">CÁLCULO MULTIVARIABLE</x:t>
         </x:is>
       </x:c>
       <x:c r="D395" s="6" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </x:c>
       <x:c r="E395" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 10-13</x:t>
+          <x:t xml:space="preserve">JU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F395" s="7" t="inlineStr">
@@ -14762,14 +14762,14 @@
       </x:c>
       <x:c r="G395" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARUJA RIVAS</x:t>
+          <x:t xml:space="preserve">HUILLCA PEDRO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA247</x:t>
+          <x:t xml:space="preserve">BEG01</x:t>
         </x:is>
       </x:c>
       <x:c r="B396" s="6" t="inlineStr">
@@ -14779,7 +14779,7 @@
       </x:c>
       <x:c r="C396" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CARTOGRAFÍA AUTOMATIZADA</x:t>
+          <x:t xml:space="preserve">ECONOMIA GENERAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D396" s="6" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </x:c>
       <x:c r="E396" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 18-20</x:t>
+          <x:t xml:space="preserve">LU 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F396" s="7" t="inlineStr">
@@ -14799,14 +14799,14 @@
       </x:c>
       <x:c r="G396" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
+          <x:t xml:space="preserve">AUBERT CÁRDENAS RUTH</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AA247</x:t>
+          <x:t xml:space="preserve">BEG01</x:t>
         </x:is>
       </x:c>
       <x:c r="B397" s="6" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </x:c>
       <x:c r="C397" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CARTOGRAFÍA AUTOMATIZADA</x:t>
+          <x:t xml:space="preserve">ECONOMIA GENERAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D397" s="6" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </x:c>
       <x:c r="E397" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 20-22</x:t>
+          <x:t xml:space="preserve">LU 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F397" s="7" t="inlineStr">
@@ -14836,14 +14836,14 @@
       </x:c>
       <x:c r="G397" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
+          <x:t xml:space="preserve">AUBERT CÁRDENAS RUTH</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH231</x:t>
+          <x:t xml:space="preserve">GE102</x:t>
         </x:is>
       </x:c>
       <x:c r="B398" s="6" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </x:c>
       <x:c r="C398" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MECANICA DE FLUIDOS</x:t>
+          <x:t xml:space="preserve">GEOGRAFÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D398" s="6" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </x:c>
       <x:c r="E398" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 17-20</x:t>
+          <x:t xml:space="preserve">LU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F398" s="7" t="inlineStr">
@@ -14873,14 +14873,14 @@
       </x:c>
       <x:c r="G398" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEJARANO OMAR</x:t>
+          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH231</x:t>
+          <x:t xml:space="preserve">GE102</x:t>
         </x:is>
       </x:c>
       <x:c r="B399" s="6" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </x:c>
       <x:c r="C399" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MECANICA DE FLUIDOS</x:t>
+          <x:t xml:space="preserve">GEOGRAFÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D399" s="6" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </x:c>
       <x:c r="E399" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 20-22</x:t>
+          <x:t xml:space="preserve">LU 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F399" s="7" t="inlineStr">
@@ -14910,14 +14910,14 @@
       </x:c>
       <x:c r="G399" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEJARANO OMAR</x:t>
+          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BO123</x:t>
+          <x:t xml:space="preserve">QU125</x:t>
         </x:is>
       </x:c>
       <x:c r="B400" s="6" t="inlineStr">
@@ -14927,7 +14927,7 @@
       </x:c>
       <x:c r="C400" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MICROBIOLOGIA Y AMBIENTE</x:t>
+          <x:t xml:space="preserve">BIOQUIMICA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D400" s="6" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </x:c>
       <x:c r="E400" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 16-17</x:t>
+          <x:t xml:space="preserve">MA 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F400" s="7" t="inlineStr">
@@ -14947,14 +14947,14 @@
       </x:c>
       <x:c r="G400" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MENDOZA ROJAS GILBERTO</x:t>
+          <x:t xml:space="preserve">MARIN HUACHACA, NELIDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BO123</x:t>
+          <x:t xml:space="preserve">QU125</x:t>
         </x:is>
       </x:c>
       <x:c r="B401" s="6" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </x:c>
       <x:c r="C401" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MICROBIOLOGIA Y AMBIENTE</x:t>
+          <x:t xml:space="preserve">BIOQUIMICA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D401" s="6" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </x:c>
       <x:c r="E401" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 11-13</x:t>
+          <x:t xml:space="preserve">VI 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F401" s="7" t="inlineStr">
@@ -14984,14 +14984,14 @@
       </x:c>
       <x:c r="G401" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SANCHEZ HEYDI</x:t>
+          <x:t xml:space="preserve">MARIN HUACHACA, NELIDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH513</x:t>
+          <x:t xml:space="preserve">FI413</x:t>
         </x:is>
       </x:c>
       <x:c r="B402" s="6" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </x:c>
       <x:c r="C402" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO ATMOSFÉRICO</x:t>
+          <x:t xml:space="preserve">FISICA III</x:t>
         </x:is>
       </x:c>
       <x:c r="D402" s="6" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </x:c>
       <x:c r="E402" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 08-10</x:t>
+          <x:t xml:space="preserve">MA 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F402" s="7" t="inlineStr">
@@ -15021,14 +15021,14 @@
       </x:c>
       <x:c r="G402" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+          <x:t xml:space="preserve">VARAS OSCAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH513</x:t>
+          <x:t xml:space="preserve">FI413</x:t>
         </x:is>
       </x:c>
       <x:c r="B403" s="6" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </x:c>
       <x:c r="C403" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO ATMOSFÉRICO</x:t>
+          <x:t xml:space="preserve">FISICA III</x:t>
         </x:is>
       </x:c>
       <x:c r="D403" s="6" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </x:c>
       <x:c r="E403" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 10-12</x:t>
+          <x:t xml:space="preserve">MI 14-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F403" s="7" t="inlineStr">
@@ -15058,14 +15058,14 @@
       </x:c>
       <x:c r="G403" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+          <x:t xml:space="preserve">VARAS OSCAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA437</x:t>
+          <x:t xml:space="preserve">PA425</x:t>
         </x:is>
       </x:c>
       <x:c r="B404" s="6" t="inlineStr">
@@ -15075,7 +15075,7 @@
       </x:c>
       <x:c r="C404" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTION DE PROYECTOS</x:t>
+          <x:t xml:space="preserve">DISEÑO Y EVALUACION DE PROYECTOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D404" s="6" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </x:c>
       <x:c r="E404" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 18-20</x:t>
+          <x:t xml:space="preserve">MI 10-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F404" s="7" t="inlineStr">
@@ -15095,14 +15095,14 @@
       </x:c>
       <x:c r="G404" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALEJOS CARLOS</x:t>
+          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA437</x:t>
+          <x:t xml:space="preserve">PA425</x:t>
         </x:is>
       </x:c>
       <x:c r="B405" s="6" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </x:c>
       <x:c r="C405" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTION DE PROYECTOS</x:t>
+          <x:t xml:space="preserve">DISEÑO Y EVALUACION DE PROYECTOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D405" s="6" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </x:c>
       <x:c r="E405" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 20-22</x:t>
+          <x:t xml:space="preserve">LU 11-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F405" s="7" t="inlineStr">
@@ -15132,14 +15132,14 @@
       </x:c>
       <x:c r="G405" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALEJOS CARLOS</x:t>
+          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH123</x:t>
+          <x:t xml:space="preserve">MA153</x:t>
         </x:is>
       </x:c>
       <x:c r="B406" s="6" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </x:c>
       <x:c r="C406" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HIDROLOGIA</x:t>
+          <x:t xml:space="preserve">ECUACIONES DIFERENCIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D406" s="6" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </x:c>
       <x:c r="E406" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 09-11</x:t>
+          <x:t xml:space="preserve">VI 08-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F406" s="7" t="inlineStr">
@@ -15169,14 +15169,14 @@
       </x:c>
       <x:c r="G406" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARTEL JAVIER</x:t>
+          <x:t xml:space="preserve">HUILLCA PEDRO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH123</x:t>
+          <x:t xml:space="preserve">MA153</x:t>
         </x:is>
       </x:c>
       <x:c r="B407" s="6" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </x:c>
       <x:c r="C407" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HIDROLOGIA</x:t>
+          <x:t xml:space="preserve">ECUACIONES DIFERENCIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D407" s="6" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </x:c>
       <x:c r="E407" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 11-13</x:t>
+          <x:t xml:space="preserve">MA 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F407" s="7" t="inlineStr">
@@ -15206,14 +15206,14 @@
       </x:c>
       <x:c r="G407" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARTEL JAVIER</x:t>
+          <x:t xml:space="preserve">HUILLCA PEDRO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS131</x:t>
+          <x:t xml:space="preserve">AS163</x:t>
         </x:is>
       </x:c>
       <x:c r="B408" s="6" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </x:c>
       <x:c r="C408" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTION SOCIAL</x:t>
+          <x:t xml:space="preserve">SOCIOLOGÍA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D408" s="6" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </x:c>
       <x:c r="E408" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 09-11</x:t>
+          <x:t xml:space="preserve">SA 09-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F408" s="7" t="inlineStr">
@@ -15243,14 +15243,14 @@
       </x:c>
       <x:c r="G408" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RIVAS MARUJA</x:t>
+          <x:t xml:space="preserve">MARUJA RIVAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS131</x:t>
+          <x:t xml:space="preserve">AS163</x:t>
         </x:is>
       </x:c>
       <x:c r="B409" s="6" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </x:c>
       <x:c r="C409" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTION SOCIAL</x:t>
+          <x:t xml:space="preserve">SOCIOLOGÍA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D409" s="6" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </x:c>
       <x:c r="E409" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 11-13</x:t>
+          <x:t xml:space="preserve">SA 10-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F409" s="7" t="inlineStr">
@@ -15280,14 +15280,14 @@
       </x:c>
       <x:c r="G409" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RIVAS MARUJA</x:t>
+          <x:t xml:space="preserve">MARUJA RIVAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FS148</x:t>
+          <x:t xml:space="preserve">AA247</x:t>
         </x:is>
       </x:c>
       <x:c r="B410" s="6" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </x:c>
       <x:c r="C410" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TERMODINÁMICA GENERAL</x:t>
+          <x:t xml:space="preserve">CARTOGRAFÍA AUTOMATIZADA</x:t>
         </x:is>
       </x:c>
       <x:c r="D410" s="6" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </x:c>
       <x:c r="E410" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 17-20</x:t>
+          <x:t xml:space="preserve">LU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F410" s="7" t="inlineStr">
@@ -15317,14 +15317,14 @@
       </x:c>
       <x:c r="G410" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEJARANO GRANDEZ OMAR</x:t>
+          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FS148</x:t>
+          <x:t xml:space="preserve">AA247</x:t>
         </x:is>
       </x:c>
       <x:c r="B411" s="6" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </x:c>
       <x:c r="C411" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TERMODINÁMICA GENERAL</x:t>
+          <x:t xml:space="preserve">CARTOGRAFÍA AUTOMATIZADA</x:t>
         </x:is>
       </x:c>
       <x:c r="D411" s="6" t="inlineStr">
@@ -15354,14 +15354,14 @@
       </x:c>
       <x:c r="G411" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BEJARANO GRANDEZ OMAR</x:t>
+          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BO152</x:t>
+          <x:t xml:space="preserve">HH231</x:t>
         </x:is>
       </x:c>
       <x:c r="B412" s="6" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </x:c>
       <x:c r="C412" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MANEJO AMBIENTAL DE LA BIODIVERSIDAD</x:t>
+          <x:t xml:space="preserve">MECANICA DE FLUIDOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D412" s="6" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </x:c>
       <x:c r="E412" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 10-13</x:t>
+          <x:t xml:space="preserve">MI 17-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F412" s="7" t="inlineStr">
@@ -15391,14 +15391,14 @@
       </x:c>
       <x:c r="G412" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARIN HUACHACA, NÉLIDA</x:t>
+          <x:t xml:space="preserve">BEJARANO OMAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BO152</x:t>
+          <x:t xml:space="preserve">HH231</x:t>
         </x:is>
       </x:c>
       <x:c r="B413" s="6" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </x:c>
       <x:c r="C413" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MANEJO AMBIENTAL DE LA BIODIVERSIDAD</x:t>
+          <x:t xml:space="preserve">MECANICA DE FLUIDOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D413" s="6" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </x:c>
       <x:c r="E413" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 14-16</x:t>
+          <x:t xml:space="preserve">MI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F413" s="7" t="inlineStr">
@@ -15428,14 +15428,14 @@
       </x:c>
       <x:c r="G413" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARIN HUACHACA, NÉLIDA</x:t>
+          <x:t xml:space="preserve">BEJARANO OMAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE111</x:t>
+          <x:t xml:space="preserve">BO123</x:t>
         </x:is>
       </x:c>
       <x:c r="B414" s="6" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </x:c>
       <x:c r="C414" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EDAFOLOGÍA</x:t>
+          <x:t xml:space="preserve">MICROBIOLOGIA Y AMBIENTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D414" s="6" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </x:c>
       <x:c r="E414" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 14-16</x:t>
+          <x:t xml:space="preserve">JU 16-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F414" s="7" t="inlineStr">
@@ -15465,14 +15465,14 @@
       </x:c>
       <x:c r="G414" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
+          <x:t xml:space="preserve">MENDOZA ROJAS GILBERTO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE111</x:t>
+          <x:t xml:space="preserve">BO123</x:t>
         </x:is>
       </x:c>
       <x:c r="B415" s="6" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </x:c>
       <x:c r="C415" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EDAFOLOGÍA</x:t>
+          <x:t xml:space="preserve">MICROBIOLOGIA Y AMBIENTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D415" s="6" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </x:c>
       <x:c r="E415" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 16-18</x:t>
+          <x:t xml:space="preserve">MI 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F415" s="7" t="inlineStr">
@@ -15502,14 +15502,14 @@
       </x:c>
       <x:c r="G415" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
+          <x:t xml:space="preserve">SANCHEZ HEYDI</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE121</x:t>
+          <x:t xml:space="preserve">HH513</x:t>
         </x:is>
       </x:c>
       <x:c r="B416" s="6" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </x:c>
       <x:c r="C416" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HIDROGEOLOGÍA</x:t>
+          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO ATMOSFÉRICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D416" s="6" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </x:c>
       <x:c r="E416" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 18-20</x:t>
+          <x:t xml:space="preserve">JU 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F416" s="7" t="inlineStr">
@@ -15539,14 +15539,14 @@
       </x:c>
       <x:c r="G416" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
+          <x:t xml:space="preserve">MATOS LIDIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE121</x:t>
+          <x:t xml:space="preserve">HH513</x:t>
         </x:is>
       </x:c>
       <x:c r="B417" s="6" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </x:c>
       <x:c r="C417" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HIDROGEOLOGÍA</x:t>
+          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO ATMOSFÉRICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D417" s="6" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </x:c>
       <x:c r="E417" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 20-22</x:t>
+          <x:t xml:space="preserve">JU 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F417" s="7" t="inlineStr">
@@ -15576,14 +15576,14 @@
       </x:c>
       <x:c r="G417" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
+          <x:t xml:space="preserve">MATOS LIDIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE131</x:t>
+          <x:t xml:space="preserve">PA437</x:t>
         </x:is>
       </x:c>
       <x:c r="B418" s="6" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </x:c>
       <x:c r="C418" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO HIDROLÓGICO</x:t>
+          <x:t xml:space="preserve">GESTION DE PROYECTOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D418" s="6" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </x:c>
       <x:c r="E418" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 08-10</x:t>
+          <x:t xml:space="preserve">JU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F418" s="7" t="inlineStr">
@@ -15613,14 +15613,14 @@
       </x:c>
       <x:c r="G418" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
+          <x:t xml:space="preserve">ALEJOS CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE131</x:t>
+          <x:t xml:space="preserve">PA437</x:t>
         </x:is>
       </x:c>
       <x:c r="B419" s="6" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </x:c>
       <x:c r="C419" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO HIDROLÓGICO</x:t>
+          <x:t xml:space="preserve">GESTION DE PROYECTOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D419" s="6" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </x:c>
       <x:c r="E419" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 10-12</x:t>
+          <x:t xml:space="preserve">JU 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F419" s="7" t="inlineStr">
@@ -15650,14 +15650,14 @@
       </x:c>
       <x:c r="G419" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
+          <x:t xml:space="preserve">ALEJOS CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AHK15</x:t>
+          <x:t xml:space="preserve">HH123</x:t>
         </x:is>
       </x:c>
       <x:c r="B420" s="6" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </x:c>
       <x:c r="C420" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACIÓN</x:t>
+          <x:t xml:space="preserve">HIDROLOGIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D420" s="6" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </x:c>
       <x:c r="E420" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 14-15</x:t>
+          <x:t xml:space="preserve">SA 09-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F420" s="7" t="inlineStr">
@@ -15687,14 +15687,14 @@
       </x:c>
       <x:c r="G420" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ETO CHERO GUADALUPE</x:t>
+          <x:t xml:space="preserve">MARTEL JAVIER</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AHK15</x:t>
+          <x:t xml:space="preserve">HH123</x:t>
         </x:is>
       </x:c>
       <x:c r="B421" s="6" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </x:c>
       <x:c r="C421" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACIÓN</x:t>
+          <x:t xml:space="preserve">HIDROLOGIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D421" s="6" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </x:c>
       <x:c r="E421" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 15-18</x:t>
+          <x:t xml:space="preserve">SA 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F421" s="7" t="inlineStr">
@@ -15724,14 +15724,14 @@
       </x:c>
       <x:c r="G421" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ETO CHERO GUADALUPE</x:t>
+          <x:t xml:space="preserve">MARTEL JAVIER</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PI121</x:t>
+          <x:t xml:space="preserve">AS131</x:t>
         </x:is>
       </x:c>
       <x:c r="B422" s="6" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </x:c>
       <x:c r="C422" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ingeniería de Procesos y Producción más Limpia</x:t>
+          <x:t xml:space="preserve">GESTION SOCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D422" s="6" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </x:c>
       <x:c r="E422" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 08-10</x:t>
+          <x:t xml:space="preserve">VI 09-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F422" s="7" t="inlineStr">
@@ -15761,14 +15761,14 @@
       </x:c>
       <x:c r="G422" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
+          <x:t xml:space="preserve">RIVAS MARUJA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PI121</x:t>
+          <x:t xml:space="preserve">AS131</x:t>
         </x:is>
       </x:c>
       <x:c r="B423" s="6" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </x:c>
       <x:c r="C423" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ingeniería de Procesos y Producción más Limpia</x:t>
+          <x:t xml:space="preserve">GESTION SOCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D423" s="6" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </x:c>
       <x:c r="E423" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 10-12</x:t>
+          <x:t xml:space="preserve">VI 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F423" s="7" t="inlineStr">
@@ -15798,14 +15798,14 @@
       </x:c>
       <x:c r="G423" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
+          <x:t xml:space="preserve">RIVAS MARUJA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE122</x:t>
+          <x:t xml:space="preserve">FS148</x:t>
         </x:is>
       </x:c>
       <x:c r="B424" s="6" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </x:c>
       <x:c r="C424" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTAMINACIÓN DEL SUELO Y TÉCNICAS DE CONTROL</x:t>
+          <x:t xml:space="preserve">TERMODINÁMICA GENERAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D424" s="6" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </x:c>
       <x:c r="E424" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 10-12</x:t>
+          <x:t xml:space="preserve">LU 17-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F424" s="7" t="inlineStr">
@@ -15835,14 +15835,14 @@
       </x:c>
       <x:c r="G424" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CELSO QUISPE</x:t>
+          <x:t xml:space="preserve">BEJARANO GRANDEZ OMAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE122</x:t>
+          <x:t xml:space="preserve">FS148</x:t>
         </x:is>
       </x:c>
       <x:c r="B425" s="6" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </x:c>
       <x:c r="C425" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTAMINACIÓN DEL SUELO Y TÉCNICAS DE CONTROL</x:t>
+          <x:t xml:space="preserve">TERMODINÁMICA GENERAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D425" s="6" t="inlineStr">
@@ -15862,7 +15862,7 @@
       </x:c>
       <x:c r="E425" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-16</x:t>
+          <x:t xml:space="preserve">LU 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F425" s="7" t="inlineStr">
@@ -15872,14 +15872,14 @@
       </x:c>
       <x:c r="G425" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CELSO QUISPE</x:t>
+          <x:t xml:space="preserve">BEJARANO GRANDEZ OMAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BO142</x:t>
+          <x:t xml:space="preserve">BO152</x:t>
         </x:is>
       </x:c>
       <x:c r="B426" s="6" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </x:c>
       <x:c r="C426" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ecotoxicología</x:t>
+          <x:t xml:space="preserve">MANEJO AMBIENTAL DE LA BIODIVERSIDAD</x:t>
         </x:is>
       </x:c>
       <x:c r="D426" s="6" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </x:c>
       <x:c r="E426" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 18-20</x:t>
+          <x:t xml:space="preserve">MA 10-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F426" s="7" t="inlineStr">
@@ -15909,14 +15909,14 @@
       </x:c>
       <x:c r="G426" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARRUFO SALDAÑA LILIANA</x:t>
+          <x:t xml:space="preserve">MARIN HUACHACA, NÉLIDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BO142</x:t>
+          <x:t xml:space="preserve">BO152</x:t>
         </x:is>
       </x:c>
       <x:c r="B427" s="6" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </x:c>
       <x:c r="C427" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ecotoxicología</x:t>
+          <x:t xml:space="preserve">MANEJO AMBIENTAL DE LA BIODIVERSIDAD</x:t>
         </x:is>
       </x:c>
       <x:c r="D427" s="6" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </x:c>
       <x:c r="E427" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 20-22</x:t>
+          <x:t xml:space="preserve">MI 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F427" s="7" t="inlineStr">
@@ -15946,14 +15946,14 @@
       </x:c>
       <x:c r="G427" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARRUFO SALDAÑA LILIANA</x:t>
+          <x:t xml:space="preserve">MARIN HUACHACA, NÉLIDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA167</x:t>
+          <x:t xml:space="preserve">GE111</x:t>
         </x:is>
       </x:c>
       <x:c r="B428" s="6" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </x:c>
       <x:c r="C428" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tratamiento de Efluentes Domésticos e Industriales</x:t>
+          <x:t xml:space="preserve">EDAFOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D428" s="6" t="inlineStr">
@@ -15973,7 +15973,7 @@
       </x:c>
       <x:c r="E428" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 17-19</x:t>
+          <x:t xml:space="preserve">JU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F428" s="7" t="inlineStr">
@@ -15983,14 +15983,14 @@
       </x:c>
       <x:c r="G428" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIROZ MIGUEL</x:t>
+          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA167</x:t>
+          <x:t xml:space="preserve">GE111</x:t>
         </x:is>
       </x:c>
       <x:c r="B429" s="6" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </x:c>
       <x:c r="C429" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tratamiento de Efluentes Domésticos e Industriales</x:t>
+          <x:t xml:space="preserve">EDAFOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D429" s="6" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </x:c>
       <x:c r="E429" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 19-21</x:t>
+          <x:t xml:space="preserve">JU 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F429" s="7" t="inlineStr">
@@ -16020,14 +16020,14 @@
       </x:c>
       <x:c r="G429" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUIROZ MIGUEL</x:t>
+          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS152</x:t>
+          <x:t xml:space="preserve">GE121</x:t>
         </x:is>
       </x:c>
       <x:c r="B430" s="6" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </x:c>
       <x:c r="C430" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Derecho Ambiental</x:t>
+          <x:t xml:space="preserve">HIDROGEOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D430" s="6" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </x:c>
       <x:c r="E430" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 09-11</x:t>
+          <x:t xml:space="preserve">VI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F430" s="7" t="inlineStr">
@@ -16057,14 +16057,14 @@
       </x:c>
       <x:c r="G430" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NEYRA CESAR</x:t>
+          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS152</x:t>
+          <x:t xml:space="preserve">GE121</x:t>
         </x:is>
       </x:c>
       <x:c r="B431" s="6" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </x:c>
       <x:c r="C431" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Derecho Ambiental</x:t>
+          <x:t xml:space="preserve">HIDROGEOLOGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D431" s="6" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </x:c>
       <x:c r="E431" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 11-13</x:t>
+          <x:t xml:space="preserve">VI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F431" s="7" t="inlineStr">
@@ -16094,14 +16094,14 @@
       </x:c>
       <x:c r="G431" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NEYRA CESAR</x:t>
+          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA152</x:t>
+          <x:t xml:space="preserve">GE131</x:t>
         </x:is>
       </x:c>
       <x:c r="B432" s="6" t="inlineStr">
@@ -16111,7 +16111,7 @@
       </x:c>
       <x:c r="C432" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SISTEMAS DE INFORMACIÓN GEOGRÁFICA</x:t>
+          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO HIDROLÓGICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D432" s="6" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </x:c>
       <x:c r="E432" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 13-15</x:t>
+          <x:t xml:space="preserve">MI 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F432" s="7" t="inlineStr">
@@ -16131,14 +16131,14 @@
       </x:c>
       <x:c r="G432" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ENRIQUE RUIZ</x:t>
+          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA152</x:t>
+          <x:t xml:space="preserve">GE131</x:t>
         </x:is>
       </x:c>
       <x:c r="B433" s="6" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </x:c>
       <x:c r="C433" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SISTEMAS DE INFORMACIÓN GEOGRÁFICA</x:t>
+          <x:t xml:space="preserve">CONTAMINACIÓN Y MODELAMIENTO HIDROLÓGICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D433" s="6" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </x:c>
       <x:c r="E433" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 15-17</x:t>
+          <x:t xml:space="preserve">MI 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F433" s="7" t="inlineStr">
@@ -16168,14 +16168,14 @@
       </x:c>
       <x:c r="G433" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ENRIQUE RUIZ</x:t>
+          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA159</x:t>
+          <x:t xml:space="preserve">AHK15</x:t>
         </x:is>
       </x:c>
       <x:c r="B434" s="6" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </x:c>
       <x:c r="C434" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VIGILANCIA Y MONITOREO DEL AMBIENTE</x:t>
+          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D434" s="6" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </x:c>
       <x:c r="E434" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 18-20</x:t>
+          <x:t xml:space="preserve">MA 14-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F434" s="7" t="inlineStr">
@@ -16205,14 +16205,14 @@
       </x:c>
       <x:c r="G434" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
+          <x:t xml:space="preserve">ETO CHERO GUADALUPE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA159</x:t>
+          <x:t xml:space="preserve">AHK15</x:t>
         </x:is>
       </x:c>
       <x:c r="B435" s="6" t="inlineStr">
@@ -16222,7 +16222,7 @@
       </x:c>
       <x:c r="C435" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VIGILANCIA Y MONITOREO DEL AMBIENTE</x:t>
+          <x:t xml:space="preserve">LIDERAZGO Y NEGOCIACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D435" s="6" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </x:c>
       <x:c r="E435" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 20-22</x:t>
+          <x:t xml:space="preserve">MA 15-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F435" s="7" t="inlineStr">
@@ -16242,24 +16242,24 @@
       </x:c>
       <x:c r="G435" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
+          <x:t xml:space="preserve">ETO CHERO GUADALUPE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA144</x:t>
+          <x:t xml:space="preserve">PI121</x:t>
         </x:is>
       </x:c>
       <x:c r="B436" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">E</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C436" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INGENIERÍA DE RESIDUOS SÓLIDOS</x:t>
+          <x:t xml:space="preserve">Ingeniería de Procesos y Producción más Limpia</x:t>
         </x:is>
       </x:c>
       <x:c r="D436" s="6" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </x:c>
       <x:c r="E436" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 18-20</x:t>
+          <x:t xml:space="preserve">VI 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F436" s="7" t="inlineStr">
@@ -16279,24 +16279,24 @@
       </x:c>
       <x:c r="G436" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CERRON PALOMINO MARCO</x:t>
+          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA144</x:t>
+          <x:t xml:space="preserve">PI121</x:t>
         </x:is>
       </x:c>
       <x:c r="B437" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">E</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C437" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INGENIERÍA DE RESIDUOS SÓLIDOS</x:t>
+          <x:t xml:space="preserve">Ingeniería de Procesos y Producción más Limpia</x:t>
         </x:is>
       </x:c>
       <x:c r="D437" s="6" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </x:c>
       <x:c r="E437" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 20-22</x:t>
+          <x:t xml:space="preserve">VI 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F437" s="7" t="inlineStr">
@@ -16316,14 +16316,14 @@
       </x:c>
       <x:c r="G437" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CERRON PALOMINO MARCO</x:t>
+          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA111</x:t>
+          <x:t xml:space="preserve">GE122</x:t>
         </x:is>
       </x:c>
       <x:c r="B438" s="6" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </x:c>
       <x:c r="C438" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ENERGÍA</x:t>
+          <x:t xml:space="preserve">CONTAMINACIÓN DEL SUELO Y TÉCNICAS DE CONTROL</x:t>
         </x:is>
       </x:c>
       <x:c r="D438" s="6" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </x:c>
       <x:c r="E438" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 16-18</x:t>
+          <x:t xml:space="preserve">LU 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F438" s="7" t="inlineStr">
@@ -16353,14 +16353,14 @@
       </x:c>
       <x:c r="G438" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NAHUI ORTIZ JOHNNY</x:t>
+          <x:t xml:space="preserve">CELSO QUISPE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA111</x:t>
+          <x:t xml:space="preserve">GE122</x:t>
         </x:is>
       </x:c>
       <x:c r="B439" s="6" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </x:c>
       <x:c r="C439" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ENERGÍA</x:t>
+          <x:t xml:space="preserve">CONTAMINACIÓN DEL SUELO Y TÉCNICAS DE CONTROL</x:t>
         </x:is>
       </x:c>
       <x:c r="D439" s="6" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </x:c>
       <x:c r="E439" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 18-20</x:t>
+          <x:t xml:space="preserve">LU 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F439" s="7" t="inlineStr">
@@ -16390,14 +16390,14 @@
       </x:c>
       <x:c r="G439" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NAHUI ORTIZ JOHNNY</x:t>
+          <x:t xml:space="preserve">CELSO QUISPE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA158</x:t>
+          <x:t xml:space="preserve">BO142</x:t>
         </x:is>
       </x:c>
       <x:c r="B440" s="6" t="inlineStr">
@@ -16407,7 +16407,7 @@
       </x:c>
       <x:c r="C440" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SIMULACIÓN Y MODELAMIENTO AMBIENTAL</x:t>
+          <x:t xml:space="preserve">Ecotoxicología</x:t>
         </x:is>
       </x:c>
       <x:c r="D440" s="6" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </x:c>
       <x:c r="E440" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 08-10</x:t>
+          <x:t xml:space="preserve">VI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F440" s="7" t="inlineStr">
@@ -16427,14 +16427,14 @@
       </x:c>
       <x:c r="G440" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PINCHE CRISTOBAL</x:t>
+          <x:t xml:space="preserve">MARRUFO SALDAÑA LILIANA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA158</x:t>
+          <x:t xml:space="preserve">BO142</x:t>
         </x:is>
       </x:c>
       <x:c r="B441" s="6" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </x:c>
       <x:c r="C441" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SIMULACIÓN Y MODELAMIENTO AMBIENTAL</x:t>
+          <x:t xml:space="preserve">Ecotoxicología</x:t>
         </x:is>
       </x:c>
       <x:c r="D441" s="6" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </x:c>
       <x:c r="E441" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 10-12</x:t>
+          <x:t xml:space="preserve">VI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F441" s="7" t="inlineStr">
@@ -16464,14 +16464,14 @@
       </x:c>
       <x:c r="G441" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PINCHE CRISTOBAL</x:t>
+          <x:t xml:space="preserve">MARRUFO SALDAÑA LILIANA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA173</x:t>
+          <x:t xml:space="preserve">GA167</x:t>
         </x:is>
       </x:c>
       <x:c r="B442" s="6" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </x:c>
       <x:c r="C442" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DISEÑO EXPERIMENTAL</x:t>
+          <x:t xml:space="preserve">Tratamiento de Efluentes Domésticos e Industriales</x:t>
         </x:is>
       </x:c>
       <x:c r="D442" s="6" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </x:c>
       <x:c r="E442" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 14-15</x:t>
+          <x:t xml:space="preserve">LU 17-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F442" s="7" t="inlineStr">
@@ -16501,14 +16501,14 @@
       </x:c>
       <x:c r="G442" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
+          <x:t xml:space="preserve">QUIROZ MIGUEL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA173</x:t>
+          <x:t xml:space="preserve">GA167</x:t>
         </x:is>
       </x:c>
       <x:c r="B443" s="6" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </x:c>
       <x:c r="C443" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DISEÑO EXPERIMENTAL</x:t>
+          <x:t xml:space="preserve">Tratamiento de Efluentes Domésticos e Industriales</x:t>
         </x:is>
       </x:c>
       <x:c r="D443" s="6" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </x:c>
       <x:c r="E443" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 15-18</x:t>
+          <x:t xml:space="preserve">LU 19-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F443" s="7" t="inlineStr">
@@ -16538,14 +16538,14 @@
       </x:c>
       <x:c r="G443" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
+          <x:t xml:space="preserve">QUIROZ MIGUEL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH515</x:t>
+          <x:t xml:space="preserve">AS152</x:t>
         </x:is>
       </x:c>
       <x:c r="B444" s="6" t="inlineStr">
@@ -16555,7 +16555,7 @@
       </x:c>
       <x:c r="C444" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INGENIERÍA DE LA CALIDAD AMBIENTAL ATMOSFÉRICA</x:t>
+          <x:t xml:space="preserve">Derecho Ambiental</x:t>
         </x:is>
       </x:c>
       <x:c r="D444" s="6" t="inlineStr">
@@ -16565,7 +16565,7 @@
       </x:c>
       <x:c r="E444" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 18-20</x:t>
+          <x:t xml:space="preserve">SA 09-11</x:t>
         </x:is>
       </x:c>
       <x:c r="F444" s="7" t="inlineStr">
@@ -16575,14 +16575,14 @@
       </x:c>
       <x:c r="G444" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PINCHE CRISTÓBAL</x:t>
+          <x:t xml:space="preserve">NEYRA CESAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HH515</x:t>
+          <x:t xml:space="preserve">AS152</x:t>
         </x:is>
       </x:c>
       <x:c r="B445" s="6" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </x:c>
       <x:c r="C445" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INGENIERÍA DE LA CALIDAD AMBIENTAL ATMOSFÉRICA</x:t>
+          <x:t xml:space="preserve">Derecho Ambiental</x:t>
         </x:is>
       </x:c>
       <x:c r="D445" s="6" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </x:c>
       <x:c r="E445" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 20-22</x:t>
+          <x:t xml:space="preserve">SA 11-13</x:t>
         </x:is>
       </x:c>
       <x:c r="F445" s="7" t="inlineStr">
@@ -16612,14 +16612,14 @@
       </x:c>
       <x:c r="G445" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PINCHE CRISTÓBAL</x:t>
+          <x:t xml:space="preserve">NEYRA CESAR</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA115</x:t>
+          <x:t xml:space="preserve">GA152</x:t>
         </x:is>
       </x:c>
       <x:c r="B446" s="6" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </x:c>
       <x:c r="C446" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PAISAJISMO Y SERVICIOS AMBIENTALES</x:t>
+          <x:t xml:space="preserve">SISTEMAS DE INFORMACIÓN GEOGRÁFICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D446" s="6" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </x:c>
       <x:c r="E446" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 14-15</x:t>
+          <x:t xml:space="preserve">VI 13-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F446" s="7" t="inlineStr">
@@ -16649,14 +16649,14 @@
       </x:c>
       <x:c r="G446" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
+          <x:t xml:space="preserve">ENRIQUE RUIZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA115</x:t>
+          <x:t xml:space="preserve">GA152</x:t>
         </x:is>
       </x:c>
       <x:c r="B447" s="6" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </x:c>
       <x:c r="C447" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PAISAJISMO Y SERVICIOS AMBIENTALES</x:t>
+          <x:t xml:space="preserve">SISTEMAS DE INFORMACIÓN GEOGRÁFICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D447" s="6" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </x:c>
       <x:c r="E447" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 16-18</x:t>
+          <x:t xml:space="preserve">VI 15-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F447" s="7" t="inlineStr">
@@ -16686,14 +16686,14 @@
       </x:c>
       <x:c r="G447" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
+          <x:t xml:space="preserve">ENRIQUE RUIZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA155</x:t>
+          <x:t xml:space="preserve">GA159</x:t>
         </x:is>
       </x:c>
       <x:c r="B448" s="6" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </x:c>
       <x:c r="C448" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ORDENAMIENTO TERRITORIAL</x:t>
+          <x:t xml:space="preserve">VIGILANCIA Y MONITOREO DEL AMBIENTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D448" s="6" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </x:c>
       <x:c r="E448" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 16-18</x:t>
+          <x:t xml:space="preserve">LU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F448" s="7" t="inlineStr">
@@ -16723,14 +16723,14 @@
       </x:c>
       <x:c r="G448" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
+          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA155</x:t>
+          <x:t xml:space="preserve">GA159</x:t>
         </x:is>
       </x:c>
       <x:c r="B449" s="6" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </x:c>
       <x:c r="C449" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ORDENAMIENTO TERRITORIAL</x:t>
+          <x:t xml:space="preserve">VIGILANCIA Y MONITOREO DEL AMBIENTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D449" s="6" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </x:c>
       <x:c r="E449" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 18-20</x:t>
+          <x:t xml:space="preserve">LU 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F449" s="7" t="inlineStr">
@@ -16760,24 +16760,24 @@
       </x:c>
       <x:c r="G449" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
+          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA163</x:t>
+          <x:t xml:space="preserve">GA144</x:t>
         </x:is>
       </x:c>
       <x:c r="B450" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">E</x:t>
         </x:is>
       </x:c>
       <x:c r="C450" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACION</x:t>
+          <x:t xml:space="preserve">INGENIERÍA DE RESIDUOS SÓLIDOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D450" s="6" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </x:c>
       <x:c r="E450" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 15-17</x:t>
+          <x:t xml:space="preserve">VI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F450" s="7" t="inlineStr">
@@ -16797,24 +16797,24 @@
       </x:c>
       <x:c r="G450" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MENDOZA ALEJANDRO</x:t>
+          <x:t xml:space="preserve">CERRON PALOMINO MARCO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA163</x:t>
+          <x:t xml:space="preserve">GA144</x:t>
         </x:is>
       </x:c>
       <x:c r="B451" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">E</x:t>
         </x:is>
       </x:c>
       <x:c r="C451" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACION</x:t>
+          <x:t xml:space="preserve">INGENIERÍA DE RESIDUOS SÓLIDOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D451" s="6" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </x:c>
       <x:c r="E451" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 17-19</x:t>
+          <x:t xml:space="preserve">VI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F451" s="7" t="inlineStr">
@@ -16834,14 +16834,14 @@
       </x:c>
       <x:c r="G451" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MENDOZA ALEJANDRO</x:t>
+          <x:t xml:space="preserve">CERRON PALOMINO MARCO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA172</x:t>
+          <x:t xml:space="preserve">GA111</x:t>
         </x:is>
       </x:c>
       <x:c r="B452" s="6" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </x:c>
       <x:c r="C452" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SISTEMAS DE GESTION AMBIENTAL</x:t>
+          <x:t xml:space="preserve">ENERGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D452" s="6" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </x:c>
       <x:c r="E452" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 18-20</x:t>
+          <x:t xml:space="preserve">JU 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F452" s="7" t="inlineStr">
@@ -16871,14 +16871,14 @@
       </x:c>
       <x:c r="G452" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA GIANNINA</x:t>
+          <x:t xml:space="preserve">NAHUI ORTIZ JOHNNY</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA172</x:t>
+          <x:t xml:space="preserve">GA111</x:t>
         </x:is>
       </x:c>
       <x:c r="B453" s="6" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </x:c>
       <x:c r="C453" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SISTEMAS DE GESTION AMBIENTAL</x:t>
+          <x:t xml:space="preserve">ENERGÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D453" s="6" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </x:c>
       <x:c r="E453" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 20-22</x:t>
+          <x:t xml:space="preserve">JU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F453" s="7" t="inlineStr">
@@ -16908,14 +16908,14 @@
       </x:c>
       <x:c r="G453" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA GIANNINA</x:t>
+          <x:t xml:space="preserve">NAHUI ORTIZ JOHNNY</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA140</x:t>
+          <x:t xml:space="preserve">GA158</x:t>
         </x:is>
       </x:c>
       <x:c r="B454" s="6" t="inlineStr">
@@ -16925,7 +16925,7 @@
       </x:c>
       <x:c r="C454" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INGENIERIA DE RECURSOS HIDRICOS</x:t>
+          <x:t xml:space="preserve">SIMULACIÓN Y MODELAMIENTO AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D454" s="6" t="inlineStr">
@@ -16935,7 +16935,7 @@
       </x:c>
       <x:c r="E454" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 14-16</x:t>
+          <x:t xml:space="preserve">SA 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F454" s="7" t="inlineStr">
@@ -16945,14 +16945,14 @@
       </x:c>
       <x:c r="G454" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CLARK HUGO NOLASCO</x:t>
+          <x:t xml:space="preserve">PINCHE CRISTOBAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA140</x:t>
+          <x:t xml:space="preserve">GA158</x:t>
         </x:is>
       </x:c>
       <x:c r="B455" s="6" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </x:c>
       <x:c r="C455" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INGENIERIA DE RECURSOS HIDRICOS</x:t>
+          <x:t xml:space="preserve">SIMULACIÓN Y MODELAMIENTO AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D455" s="6" t="inlineStr">
@@ -16972,7 +16972,7 @@
       </x:c>
       <x:c r="E455" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 16-18</x:t>
+          <x:t xml:space="preserve">SA 10-12</x:t>
         </x:is>
       </x:c>
       <x:c r="F455" s="7" t="inlineStr">
@@ -16982,14 +16982,14 @@
       </x:c>
       <x:c r="G455" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CLARK HUGO NOLASCO</x:t>
+          <x:t xml:space="preserve">PINCHE CRISTOBAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA931</x:t>
+          <x:t xml:space="preserve">GA173</x:t>
         </x:is>
       </x:c>
       <x:c r="B456" s="6" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </x:c>
       <x:c r="C456" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
+          <x:t xml:space="preserve">DISEÑO EXPERIMENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D456" s="6" t="inlineStr">
@@ -17009,7 +17009,7 @@
       </x:c>
       <x:c r="E456" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 19-21</x:t>
+          <x:t xml:space="preserve">VI 14-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F456" s="7" t="inlineStr">
@@ -17019,14 +17019,14 @@
       </x:c>
       <x:c r="G456" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
+          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA931</x:t>
+          <x:t xml:space="preserve">GA173</x:t>
         </x:is>
       </x:c>
       <x:c r="B457" s="6" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </x:c>
       <x:c r="C457" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
+          <x:t xml:space="preserve">DISEÑO EXPERIMENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D457" s="6" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </x:c>
       <x:c r="E457" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 21-22</x:t>
+          <x:t xml:space="preserve">VI 15-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F457" s="7" t="inlineStr">
@@ -17056,14 +17056,14 @@
       </x:c>
       <x:c r="G457" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
+          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA931</x:t>
+          <x:t xml:space="preserve">HH515</x:t>
         </x:is>
       </x:c>
       <x:c r="B458" s="6" t="inlineStr">
@@ -17073,17 +17073,17 @@
       </x:c>
       <x:c r="C458" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
+          <x:t xml:space="preserve">INGENIERÍA DE LA CALIDAD AMBIENTAL ATMOSFÉRICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D458" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E458" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 08-10</x:t>
+          <x:t xml:space="preserve">MI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F458" s="7" t="inlineStr">
@@ -17093,14 +17093,14 @@
       </x:c>
       <x:c r="G458" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
+          <x:t xml:space="preserve">PINCHE CRISTÓBAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA174</x:t>
+          <x:t xml:space="preserve">HH515</x:t>
         </x:is>
       </x:c>
       <x:c r="B459" s="6" t="inlineStr">
@@ -17110,17 +17110,17 @@
       </x:c>
       <x:c r="C459" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
+          <x:t xml:space="preserve">INGENIERÍA DE LA CALIDAD AMBIENTAL ATMOSFÉRICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D459" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E459" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 18-20</x:t>
+          <x:t xml:space="preserve">MI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F459" s="7" t="inlineStr">
@@ -17130,14 +17130,14 @@
       </x:c>
       <x:c r="G459" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
+          <x:t xml:space="preserve">PINCHE CRISTÓBAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA174</x:t>
+          <x:t xml:space="preserve">GA115</x:t>
         </x:is>
       </x:c>
       <x:c r="B460" s="6" t="inlineStr">
@@ -17147,17 +17147,17 @@
       </x:c>
       <x:c r="C460" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
+          <x:t xml:space="preserve">PAISAJISMO Y SERVICIOS AMBIENTALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D460" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E460" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 20-22</x:t>
+          <x:t xml:space="preserve">MI 14-15</x:t>
         </x:is>
       </x:c>
       <x:c r="F460" s="7" t="inlineStr">
@@ -17167,34 +17167,34 @@
       </x:c>
       <x:c r="G460" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
+          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA175</x:t>
+          <x:t xml:space="preserve">GA115</x:t>
         </x:is>
       </x:c>
       <x:c r="B461" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">J</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C461" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
+          <x:t xml:space="preserve">PAISAJISMO Y SERVICIOS AMBIENTALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D461" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E461" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 18-20</x:t>
+          <x:t xml:space="preserve">MI 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F461" s="7" t="inlineStr">
@@ -17204,34 +17204,34 @@
       </x:c>
       <x:c r="G461" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQUENA NORVIN</x:t>
+          <x:t xml:space="preserve">ALIAGA MARIA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA175</x:t>
+          <x:t xml:space="preserve">GA155</x:t>
         </x:is>
       </x:c>
       <x:c r="B462" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">J</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C462" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
+          <x:t xml:space="preserve">ORDENAMIENTO TERRITORIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D462" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E462" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 20-22</x:t>
+          <x:t xml:space="preserve">MA 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F462" s="7" t="inlineStr">
@@ -17241,34 +17241,34 @@
       </x:c>
       <x:c r="G462" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQUENA NORVIN</x:t>
+          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA174</x:t>
+          <x:t xml:space="preserve">GA155</x:t>
         </x:is>
       </x:c>
       <x:c r="B463" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">M</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C463" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
+          <x:t xml:space="preserve">ORDENAMIENTO TERRITORIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D463" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E463" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 20-22</x:t>
+          <x:t xml:space="preserve">MA 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F463" s="7" t="inlineStr">
@@ -17278,29 +17278,29 @@
       </x:c>
       <x:c r="G463" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
+          <x:t xml:space="preserve">VELASQUEZ WENDER</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA174</x:t>
+          <x:t xml:space="preserve">GA163</x:t>
         </x:is>
       </x:c>
       <x:c r="B464" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">M</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C464" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
+          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACION</x:t>
         </x:is>
       </x:c>
       <x:c r="D464" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E464" s="6" t="inlineStr">
@@ -17315,14 +17315,14 @@
       </x:c>
       <x:c r="G464" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
+          <x:t xml:space="preserve">MENDOZA ALEJANDRO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA135</x:t>
+          <x:t xml:space="preserve">GA163</x:t>
         </x:is>
       </x:c>
       <x:c r="B465" s="6" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </x:c>
       <x:c r="C465" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN DE DESASTRES</x:t>
+          <x:t xml:space="preserve">TALLER DE PROYECTO DE INVESTIGACION</x:t>
         </x:is>
       </x:c>
       <x:c r="D465" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E465" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 14-16</x:t>
+          <x:t xml:space="preserve">VI 17-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F465" s="7" t="inlineStr">
@@ -17352,14 +17352,14 @@
       </x:c>
       <x:c r="G465" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA</x:t>
+          <x:t xml:space="preserve">MENDOZA ALEJANDRO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA135</x:t>
+          <x:t xml:space="preserve">GA172</x:t>
         </x:is>
       </x:c>
       <x:c r="B466" s="6" t="inlineStr">
@@ -17369,17 +17369,17 @@
       </x:c>
       <x:c r="C466" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN DE DESASTRES</x:t>
+          <x:t xml:space="preserve">SISTEMAS DE GESTION AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D466" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E466" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MA 16-18</x:t>
+          <x:t xml:space="preserve">JU 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F466" s="7" t="inlineStr">
@@ -17389,14 +17389,14 @@
       </x:c>
       <x:c r="G466" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA</x:t>
+          <x:t xml:space="preserve">ARANA GIANNINA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA439</x:t>
+          <x:t xml:space="preserve">GA172</x:t>
         </x:is>
       </x:c>
       <x:c r="B467" s="6" t="inlineStr">
@@ -17406,17 +17406,17 @@
       </x:c>
       <x:c r="C467" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FINANZAS AMBIENTALES</x:t>
+          <x:t xml:space="preserve">SISTEMAS DE GESTION AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D467" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E467" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 17-18</x:t>
+          <x:t xml:space="preserve">JU 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F467" s="7" t="inlineStr">
@@ -17426,14 +17426,14 @@
       </x:c>
       <x:c r="G467" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
+          <x:t xml:space="preserve">ARANA GIANNINA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA439</x:t>
+          <x:t xml:space="preserve">GA140</x:t>
         </x:is>
       </x:c>
       <x:c r="B468" s="6" t="inlineStr">
@@ -17443,17 +17443,17 @@
       </x:c>
       <x:c r="C468" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FINANZAS AMBIENTALES</x:t>
+          <x:t xml:space="preserve">INGENIERIA DE RECURSOS HIDRICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D468" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E468" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 18-21</x:t>
+          <x:t xml:space="preserve">SA 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F468" s="7" t="inlineStr">
@@ -17463,14 +17463,14 @@
       </x:c>
       <x:c r="G468" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
+          <x:t xml:space="preserve">CLARK HUGO NOLASCO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA177</x:t>
+          <x:t xml:space="preserve">GA140</x:t>
         </x:is>
       </x:c>
       <x:c r="B469" s="6" t="inlineStr">
@@ -17480,17 +17480,17 @@
       </x:c>
       <x:c r="C469" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISCALIZACION Y AUDITORIA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">INGENIERIA DE RECURSOS HIDRICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D469" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E469" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 16-18</x:t>
+          <x:t xml:space="preserve">SA 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F469" s="7" t="inlineStr">
@@ -17500,14 +17500,14 @@
       </x:c>
       <x:c r="G469" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JORGE MIRANDA</x:t>
+          <x:t xml:space="preserve">CLARK HUGO NOLASCO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA177</x:t>
+          <x:t xml:space="preserve">SA931</x:t>
         </x:is>
       </x:c>
       <x:c r="B470" s="6" t="inlineStr">
@@ -17517,17 +17517,17 @@
       </x:c>
       <x:c r="C470" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FISCALIZACION Y AUDITORIA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
         </x:is>
       </x:c>
       <x:c r="D470" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
+          <x:t xml:space="preserve">TEORIA</x:t>
         </x:is>
       </x:c>
       <x:c r="E470" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MI 18-20</x:t>
+          <x:t xml:space="preserve">MI 19-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F470" s="7" t="inlineStr">
@@ -17537,14 +17537,14 @@
       </x:c>
       <x:c r="G470" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JORGE MIRANDA</x:t>
+          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA137</x:t>
+          <x:t xml:space="preserve">SA931</x:t>
         </x:is>
       </x:c>
       <x:c r="B471" s="6" t="inlineStr">
@@ -17554,17 +17554,17 @@
       </x:c>
       <x:c r="C471" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALORACIÓN ECONÓMICA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
         </x:is>
       </x:c>
       <x:c r="D471" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
+          <x:t xml:space="preserve">PRACTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="E471" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 17-18</x:t>
+          <x:t xml:space="preserve">MI 21-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F471" s="7" t="inlineStr">
@@ -17574,14 +17574,14 @@
       </x:c>
       <x:c r="G471" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
+          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA137</x:t>
+          <x:t xml:space="preserve">SA931</x:t>
         </x:is>
       </x:c>
       <x:c r="B472" s="6" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </x:c>
       <x:c r="C472" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALORACIÓN ECONÓMICA AMBIENTAL</x:t>
+          <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
         </x:is>
       </x:c>
       <x:c r="D472" s="6" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </x:c>
       <x:c r="E472" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 18-21</x:t>
+          <x:t xml:space="preserve">SA 08-10</x:t>
         </x:is>
       </x:c>
       <x:c r="F472" s="7" t="inlineStr">
@@ -17611,14 +17611,14 @@
       </x:c>
       <x:c r="G472" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
+          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS133</x:t>
+          <x:t xml:space="preserve">GA174</x:t>
         </x:is>
       </x:c>
       <x:c r="B473" s="6" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </x:c>
       <x:c r="C473" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RESPONSABILIDAD SOCIAL</x:t>
+          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D473" s="6" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </x:c>
       <x:c r="E473" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 14-16</x:t>
+          <x:t xml:space="preserve">MA 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F473" s="7" t="inlineStr">
@@ -17648,14 +17648,14 @@
       </x:c>
       <x:c r="G473" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ETO GUADALUPE</x:t>
+          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AS133</x:t>
+          <x:t xml:space="preserve">GA174</x:t>
         </x:is>
       </x:c>
       <x:c r="B474" s="6" t="inlineStr">
@@ -17665,7 +17665,7 @@
       </x:c>
       <x:c r="C474" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RESPONSABILIDAD SOCIAL</x:t>
+          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D474" s="6" t="inlineStr">
@@ -17675,7 +17675,7 @@
       </x:c>
       <x:c r="E474" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 16-18</x:t>
+          <x:t xml:space="preserve">MA 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F474" s="7" t="inlineStr">
@@ -17685,24 +17685,24 @@
       </x:c>
       <x:c r="G474" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ETO GUADALUPE</x:t>
+          <x:t xml:space="preserve">RUIZ NAZARIO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE133</x:t>
+          <x:t xml:space="preserve">GA175</x:t>
         </x:is>
       </x:c>
       <x:c r="B475" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">J</x:t>
         </x:is>
       </x:c>
       <x:c r="C475" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTROL DE LA DESERTIFICACION</x:t>
+          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D475" s="6" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </x:c>
       <x:c r="E475" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 09-11</x:t>
+          <x:t xml:space="preserve">MA 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F475" s="7" t="inlineStr">
@@ -17722,24 +17722,24 @@
       </x:c>
       <x:c r="G475" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
+          <x:t xml:space="preserve">REQUENA NORVIN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE133</x:t>
+          <x:t xml:space="preserve">GA175</x:t>
         </x:is>
       </x:c>
       <x:c r="B476" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">J</x:t>
         </x:is>
       </x:c>
       <x:c r="C476" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CONTROL DE LA DESERTIFICACION</x:t>
+          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D476" s="6" t="inlineStr">
@@ -17749,7 +17749,7 @@
       </x:c>
       <x:c r="E476" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 11-13</x:t>
+          <x:t xml:space="preserve">MA 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F476" s="7" t="inlineStr">
@@ -17759,24 +17759,24 @@
       </x:c>
       <x:c r="G476" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
+          <x:t xml:space="preserve">REQUENA NORVIN</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE132G</x:t>
+          <x:t xml:space="preserve">GA174</x:t>
         </x:is>
       </x:c>
       <x:c r="B477" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">M</x:t>
         </x:is>
       </x:c>
       <x:c r="C477" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CAMBIO CLIMÁTICO</x:t>
+          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D477" s="6" t="inlineStr">
@@ -17786,7 +17786,7 @@
       </x:c>
       <x:c r="E477" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-16</x:t>
+          <x:t xml:space="preserve">MI 20-22</x:t>
         </x:is>
       </x:c>
       <x:c r="F477" s="7" t="inlineStr">
@@ -17796,24 +17796,24 @@
       </x:c>
       <x:c r="G477" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GE132G</x:t>
+          <x:t xml:space="preserve">GA174</x:t>
         </x:is>
       </x:c>
       <x:c r="B478" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">G</x:t>
+          <x:t xml:space="preserve">M</x:t>
         </x:is>
       </x:c>
       <x:c r="C478" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CAMBIO CLIMÁTICO</x:t>
+          <x:t xml:space="preserve">TALLER DE INVESTIGACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D478" s="6" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </x:c>
       <x:c r="E478" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 16-18</x:t>
+          <x:t xml:space="preserve">VI 15-17</x:t>
         </x:is>
       </x:c>
       <x:c r="F478" s="7" t="inlineStr">
@@ -17833,24 +17833,24 @@
       </x:c>
       <x:c r="G478" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+          <x:t xml:space="preserve">NAHUI JOHNNY</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA140</x:t>
+          <x:t xml:space="preserve">GA135</x:t>
         </x:is>
       </x:c>
       <x:c r="B479" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">F</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C479" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN EMPRESARIAL</x:t>
+          <x:t xml:space="preserve">GESTIÓN DE DESASTRES</x:t>
         </x:is>
       </x:c>
       <x:c r="D479" s="6" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </x:c>
       <x:c r="E479" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 14-15</x:t>
+          <x:t xml:space="preserve">MA 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F479" s="7" t="inlineStr">
@@ -17870,24 +17870,24 @@
       </x:c>
       <x:c r="G479" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALDIVIA MALDONADO PEDRO</x:t>
+          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PA140</x:t>
+          <x:t xml:space="preserve">GA135</x:t>
         </x:is>
       </x:c>
       <x:c r="B480" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">F</x:t>
+          <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
       <x:c r="C480" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN EMPRESARIAL</x:t>
+          <x:t xml:space="preserve">GESTIÓN DE DESASTRES</x:t>
         </x:is>
       </x:c>
       <x:c r="D480" s="6" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </x:c>
       <x:c r="E480" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 14-16</x:t>
+          <x:t xml:space="preserve">MA 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F480" s="7" t="inlineStr">
@@ -17907,14 +17907,14 @@
       </x:c>
       <x:c r="G480" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VALDIVIA MALDONADO PEDRO</x:t>
+          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA175</x:t>
+          <x:t xml:space="preserve">PA439</x:t>
         </x:is>
       </x:c>
       <x:c r="B481" s="6" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </x:c>
       <x:c r="C481" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECOEFICIENCIA</x:t>
+          <x:t xml:space="preserve">FINANZAS AMBIENTALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D481" s="6" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </x:c>
       <x:c r="E481" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 14-16</x:t>
+          <x:t xml:space="preserve">LU 17-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F481" s="7" t="inlineStr">
@@ -17944,14 +17944,14 @@
       </x:c>
       <x:c r="G481" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
+          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA175</x:t>
+          <x:t xml:space="preserve">PA439</x:t>
         </x:is>
       </x:c>
       <x:c r="B482" s="6" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </x:c>
       <x:c r="C482" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ECOEFICIENCIA</x:t>
+          <x:t xml:space="preserve">FINANZAS AMBIENTALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D482" s="6" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </x:c>
       <x:c r="E482" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 16-18</x:t>
+          <x:t xml:space="preserve">LU 18-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F482" s="7" t="inlineStr">
@@ -17981,14 +17981,14 @@
       </x:c>
       <x:c r="G482" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
+          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA178</x:t>
+          <x:t xml:space="preserve">GA177</x:t>
         </x:is>
       </x:c>
       <x:c r="B483" s="6" t="inlineStr">
@@ -17998,7 +17998,7 @@
       </x:c>
       <x:c r="C483" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN DE LA CALIDAD</x:t>
+          <x:t xml:space="preserve">FISCALIZACION Y AUDITORIA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D483" s="6" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </x:c>
       <x:c r="E483" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 14-16</x:t>
+          <x:t xml:space="preserve">MI 16-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F483" s="7" t="inlineStr">
@@ -18018,14 +18018,14 @@
       </x:c>
       <x:c r="G483" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARTEL JAVIER EDWIN</x:t>
+          <x:t xml:space="preserve">JORGE MIRANDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GA178</x:t>
+          <x:t xml:space="preserve">GA177</x:t>
         </x:is>
       </x:c>
       <x:c r="B484" s="6" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </x:c>
       <x:c r="C484" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTIÓN DE LA CALIDAD</x:t>
+          <x:t xml:space="preserve">FISCALIZACION Y AUDITORIA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D484" s="6" t="inlineStr">
@@ -18045,7 +18045,7 @@
       </x:c>
       <x:c r="E484" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA 16-18</x:t>
+          <x:t xml:space="preserve">MI 18-20</x:t>
         </x:is>
       </x:c>
       <x:c r="F484" s="7" t="inlineStr">
@@ -18055,14 +18055,14 @@
       </x:c>
       <x:c r="G484" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MARTEL JAVIER EDWIN</x:t>
+          <x:t xml:space="preserve">JORGE MIRANDA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA846</x:t>
+          <x:t xml:space="preserve">GA137</x:t>
         </x:is>
       </x:c>
       <x:c r="B485" s="6" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </x:c>
       <x:c r="C485" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTION DE LA SEGURIDAD Y SALUD OCUPACIONAL</x:t>
+          <x:t xml:space="preserve">VALORACIÓN ECONÓMICA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D485" s="6" t="inlineStr">
@@ -18082,7 +18082,7 @@
       </x:c>
       <x:c r="E485" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 18-20</x:t>
+          <x:t xml:space="preserve">VI 17-18</x:t>
         </x:is>
       </x:c>
       <x:c r="F485" s="7" t="inlineStr">
@@ -18092,14 +18092,14 @@
       </x:c>
       <x:c r="G485" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA JESÚS</x:t>
+          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SA846</x:t>
+          <x:t xml:space="preserve">GA137</x:t>
         </x:is>
       </x:c>
       <x:c r="B486" s="6" t="inlineStr">
@@ -18109,7 +18109,7 @@
       </x:c>
       <x:c r="C486" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GESTION DE LA SEGURIDAD Y SALUD OCUPACIONAL</x:t>
+          <x:t xml:space="preserve">VALORACIÓN ECONÓMICA AMBIENTAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D486" s="6" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </x:c>
       <x:c r="E486" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JU 20-22</x:t>
+          <x:t xml:space="preserve">VI 18-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F486" s="7" t="inlineStr">
@@ -18129,14 +18129,14 @@
       </x:c>
       <x:c r="G486" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA JESÚS</x:t>
+          <x:t xml:space="preserve">COLLAZOS CERRON JESUS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BO151</x:t>
+          <x:t xml:space="preserve">AS133</x:t>
         </x:is>
       </x:c>
       <x:c r="B487" s="6" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </x:c>
       <x:c r="C487" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BIOTECNOLOGÍA</x:t>
+          <x:t xml:space="preserve">RESPONSABILIDAD SOCIAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D487" s="6" t="inlineStr">
@@ -18156,7 +18156,7 @@
       </x:c>
       <x:c r="E487" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">LU 10-12</x:t>
+          <x:t xml:space="preserve">VI 14-16</x:t>
         </x:is>
       </x:c>
       <x:c r="F487" s="7" t="inlineStr">
@@ -18166,42 +18166,560 @@
       </x:c>
       <x:c r="G487" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SANCHEZ TORRES HEIDI</x:t>
+          <x:t xml:space="preserve">ETO GUADALUPE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="6" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">AS133</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B488" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C488" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RESPONSABILIDAD SOCIAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D488" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E488" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VI 16-18</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F488" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G488" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ETO GUADALUPE</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GE133</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B489" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C489" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CONTROL DE LA DESERTIFICACION</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D489" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E489" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VI 09-11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F489" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G489" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GE133</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B490" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C490" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CONTROL DE LA DESERTIFICACION</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D490" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E490" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VI 11-13</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F490" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G490" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QUISPE OJEDA CELSO</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GE132G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B491" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C491" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CAMBIO CLIMÁTICO</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D491" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E491" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LU 14-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F491" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G491" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GE132G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B492" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C492" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CAMBIO CLIMÁTICO</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D492" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E492" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LU 16-18</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F492" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G492" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MATOS LIDIO</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PA140</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B493" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">F</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C493" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GESTIÓN EMPRESARIAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D493" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E493" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LU 14-15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F493" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G493" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VALDIVIA MALDONADO PEDRO</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PA140</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B494" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">F</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C494" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GESTIÓN EMPRESARIAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D494" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E494" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JU 14-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F494" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G494" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VALDIVIA MALDONADO PEDRO</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GA175</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B495" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C495" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECOEFICIENCIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D495" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E495" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SA 14-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F495" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G495" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GA175</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B496" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C496" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECOEFICIENCIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D496" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E496" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SA 16-18</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F496" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G496" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ARANA OCHOA GIANINNA</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GA178</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B497" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C497" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GESTIÓN DE LA CALIDAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D497" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E497" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SA 14-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F497" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G497" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MARTEL JAVIER EDWIN</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GA178</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B498" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C498" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GESTIÓN DE LA CALIDAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D498" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E498" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SA 16-18</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F498" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G498" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MARTEL JAVIER EDWIN</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SA846</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B499" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C499" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GESTION DE LA SEGURIDAD Y SALUD OCUPACIONAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D499" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E499" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JU 18-20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F499" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G499" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA JESÚS</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SA846</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B500" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C500" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GESTION DE LA SEGURIDAD Y SALUD OCUPACIONAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D500" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E500" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JU 20-22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F500" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G500" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">HERNANDEZ CARRILLO MARIA JESÚS</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="501">
+      <x:c r="A501" s="6" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">BO151</x:t>
         </x:is>
       </x:c>
-      <x:c r="B488" s="6" t="inlineStr">
+      <x:c r="B501" s="6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">G</x:t>
         </x:is>
       </x:c>
-      <x:c r="C488" s="6" t="inlineStr">
+      <x:c r="C501" s="6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">BIOTECNOLOGÍA</x:t>
         </x:is>
       </x:c>
-      <x:c r="D488" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E488" s="6" t="inlineStr">
+      <x:c r="D501" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E501" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LU 10-12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F501" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G501" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SANCHEZ TORRES HEIDI</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="502">
+      <x:c r="A502" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BO151</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B502" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">G</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C502" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BIOTECNOLOGÍA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D502" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E502" s="6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MA 09-11</x:t>
         </x:is>
       </x:c>
-      <x:c r="F488" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G488" s="7" t="inlineStr">
+      <x:c r="F502" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G502" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SANCHEZ TORRES HEIDI</x:t>
         </x:is>
@@ -18236,7 +18754,7 @@
       </x:c>
       <x:c r="B1" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HORARIOS 26-2 (2).xlsx</x:t>
+          <x:t xml:space="preserve">HORARIOS 26-2.xlsx</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -18247,7 +18765,7 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="0" t="n">
-        <x:v>484</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -18270,7 +18788,7 @@
       </x:c>
       <x:c r="B4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HORARIOS 26-2 (2).xlsx</x:t>
+          <x:t xml:space="preserve">HORARIOS 26-2.xlsx</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/FIA2026-2.xlsx
+++ b/FIA2026-2.xlsx
@@ -245,7 +245,7 @@
     <x:row r="2">
       <x:c r="A2" s="3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Extraído de: HORARIOS 26-2.xlsx</x:t>
+          <x:t xml:space="preserve">Extraído de: HORARIOS 26-2 (1).xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" s="2" t="n"/>
@@ -2283,7 +2283,7 @@
       </x:c>
       <x:c r="E58" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 16-21</x:t>
+          <x:t xml:space="preserve">VI 18-21</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="7" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </x:c>
       <x:c r="E141" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VI 16-19</x:t>
+          <x:t xml:space="preserve">MI 16-19</x:t>
         </x:is>
       </x:c>
       <x:c r="F141" s="7" t="inlineStr">
@@ -17517,27 +17517,27 @@
       </x:c>
       <x:c r="C470" s="6" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SISTEMAS DE EVALUACIÓN DE IMPACTO AMBIENTAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D470" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TEORIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E470" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MI 19-21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F470" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G470" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D470" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TEORIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E470" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MI 19-21</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F470" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G470" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -17554,27 +17554,27 @@
       </x:c>
       <x:c r="C471" s="6" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SISTEMAS DE EVALUACIÓN DE IMPACTO AMBIENTAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D471" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E471" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MI 21-22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F471" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G471" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D471" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E471" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MI 21-22</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F471" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G471" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -17591,27 +17591,27 @@
       </x:c>
       <x:c r="C472" s="6" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">SISTEMAS DE EVALUACIÓN DE IMPACTO AMBIENTAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D472" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PRACTICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E472" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SA 08-10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F472" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G472" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">VALER CERNA KARLA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D472" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PRACTICA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E472" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SA 08-10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F472" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G472" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ALVA HUAPAYA CARLOS</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -18754,7 +18754,7 @@
       </x:c>
       <x:c r="B1" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HORARIOS 26-2.xlsx</x:t>
+          <x:t xml:space="preserve">HORARIOS 26-2 (1).xlsx</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -18788,7 +18788,7 @@
       </x:c>
       <x:c r="B4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HORARIOS 26-2.xlsx</x:t>
+          <x:t xml:space="preserve">HORARIOS 26-2 (1).xlsx</x:t>
         </x:is>
       </x:c>
     </x:row>
